--- a/BGG桌遊資料_完整.xlsx
+++ b/BGG桌遊資料_完整.xlsx
@@ -1,8 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BGG完整清單" sheetId="1" r:id="Rc957422170944b0a"/>
+    <x:sheet name="BGG完整清單" sheetId="1" r:id="Rc957422170944b0a"/>
+    <x:sheet name="設計師資料" sheetId="2" r:id="rIdDesigner2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -12430,4 +12431,5963 @@
     <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4620240f087d41d4"/>
   </x:tableParts>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:dimension ref="A1:O133"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="30" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="32" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="30" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="55" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="60" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="42" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="16" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="60" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="55" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="20" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="60" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="55" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="38" customHeight="1">
+      <x:c r="A1" s="21" t="str">
+        <x:v>設計師名稱</x:v>
+      </x:c>
+      <x:c r="B1" s="21" t="str">
+        <x:v>設計師索引鍵</x:v>
+      </x:c>
+      <x:c r="C1" s="21" t="str">
+        <x:v>BGG 設計師 ID</x:v>
+      </x:c>
+      <x:c r="D1" s="21" t="str">
+        <x:v>BGG 設計師名稱</x:v>
+      </x:c>
+      <x:c r="E1" s="21" t="str">
+        <x:v>BGG 設計師頁 URL</x:v>
+      </x:c>
+      <x:c r="F1" s="21" t="str">
+        <x:v>照片來源 URL</x:v>
+      </x:c>
+      <x:c r="G1" s="21" t="str">
+        <x:v>網站照片路徑</x:v>
+      </x:c>
+      <x:c r="H1" s="21" t="str">
+        <x:v>BGG 圖片 ID</x:v>
+      </x:c>
+      <x:c r="I1" s="21" t="str">
+        <x:v>照片查核狀態</x:v>
+      </x:c>
+      <x:c r="J1" s="21" t="str">
+        <x:v>查核日期</x:v>
+      </x:c>
+      <x:c r="K1" s="21" t="str">
+        <x:v>BGG 中繼資料 URL</x:v>
+      </x:c>
+      <x:c r="L1" s="21" t="str">
+        <x:v>身分核對遊戲 URL</x:v>
+      </x:c>
+      <x:c r="M1" s="21" t="str">
+        <x:v>身分核對遊戲 ID</x:v>
+      </x:c>
+      <x:c r="N1" s="21" t="str">
+        <x:v>身分核對中繼資料 URL</x:v>
+      </x:c>
+      <x:c r="O1" s="21" t="str">
+        <x:v>查核備註</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="22" customHeight="1">
+      <x:c r="A2" s="34" t="str">
+        <x:v>Adam E. Daulton</x:v>
+      </x:c>
+      <x:c r="B2" s="34" t="str">
+        <x:v>adam e. daulton</x:v>
+      </x:c>
+      <x:c r="C2" s="34" t="str">
+        <x:v>62465</x:v>
+      </x:c>
+      <x:c r="D2" s="34" t="str">
+        <x:v>Adam E. Daulton</x:v>
+      </x:c>
+      <x:c r="E2" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/62465/adam-e-daulton</x:v>
+      </x:c>
+      <x:c r="F2" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/oAL-whf9aw1y41NvF6tSqg__previewthumb/img/MVpaa-kLHEbEjSojP8DQzt1gYRI=/fit-in/300x320/filters:strip_icc()/pic2608474.jpg</x:v>
+      </x:c>
+      <x:c r="G2" s="34" t="str">
+        <x:v>assets/designers/62465.webp</x:v>
+      </x:c>
+      <x:c r="H2" s="34" t="str">
+        <x:v>2608474</x:v>
+      </x:c>
+      <x:c r="I2" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J2" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K2" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=62465&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L2" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/341974/power-plants</x:v>
+      </x:c>
+      <x:c r="M2" s="34" t="str">
+        <x:v>341974</x:v>
+      </x:c>
+      <x:c r="N2" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=341974&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O2" s="34" t="str"/>
+    </x:row>
+    <x:row r="3" ht="22" customHeight="1">
+      <x:c r="A3" s="34" t="str">
+        <x:v>Adam Španěl</x:v>
+      </x:c>
+      <x:c r="B3" s="34" t="str">
+        <x:v>adam španěl</x:v>
+      </x:c>
+      <x:c r="C3" s="34" t="str">
+        <x:v>111991</x:v>
+      </x:c>
+      <x:c r="D3" s="34" t="str">
+        <x:v>Adam Španěl</x:v>
+      </x:c>
+      <x:c r="E3" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/111991/adam-spanel</x:v>
+      </x:c>
+      <x:c r="F3" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/7zreeug9shBZOhNTvHbIRA__previewthumb/img/krsHmUuzLDGSJhRJeMD3drkGH64=/fit-in/300x320/filters:strip_icc()/pic9766387.jpg</x:v>
+      </x:c>
+      <x:c r="G3" s="34" t="str">
+        <x:v>assets/designers/111991.webp</x:v>
+      </x:c>
+      <x:c r="H3" s="34" t="str">
+        <x:v>9766387</x:v>
+      </x:c>
+      <x:c r="I3" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J3" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K3" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=111991&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L3" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/465669/drillers</x:v>
+      </x:c>
+      <x:c r="M3" s="34" t="str">
+        <x:v>465669</x:v>
+      </x:c>
+      <x:c r="N3" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=465669&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O3" s="34" t="str"/>
+    </x:row>
+    <x:row r="4" ht="22" customHeight="1">
+      <x:c r="A4" s="34" t="str">
+        <x:v>Adrian Adamescu</x:v>
+      </x:c>
+      <x:c r="B4" s="34" t="str">
+        <x:v>adrian adamescu</x:v>
+      </x:c>
+      <x:c r="C4" s="34" t="str">
+        <x:v>88370</x:v>
+      </x:c>
+      <x:c r="D4" s="34" t="str">
+        <x:v>Adrian Adamescu</x:v>
+      </x:c>
+      <x:c r="E4" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/88370/adrian-adamescu</x:v>
+      </x:c>
+      <x:c r="F4" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/RDZJI1RVZcb53WwVaRAG9Q__previewthumb/img/o7dPnsM_CeDiHp1gN8H_DxWZROI=/fit-in/300x320/filters:strip_icc()/pic2844249.jpg</x:v>
+      </x:c>
+      <x:c r="G4" s="34" t="str">
+        <x:v>assets/designers/88370.webp</x:v>
+      </x:c>
+      <x:c r="H4" s="34" t="str">
+        <x:v>2844249</x:v>
+      </x:c>
+      <x:c r="I4" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J4" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K4" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=88370&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L4" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/466710</x:v>
+      </x:c>
+      <x:c r="M4" s="34" t="str">
+        <x:v>466710</x:v>
+      </x:c>
+      <x:c r="N4" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=466710&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O4" s="34" t="str"/>
+    </x:row>
+    <x:row r="5" ht="22" customHeight="1">
+      <x:c r="A5" s="34" t="str">
+        <x:v>Aiollus</x:v>
+      </x:c>
+      <x:c r="B5" s="34" t="str">
+        <x:v>aiollus</x:v>
+      </x:c>
+      <x:c r="C5" s="34" t="str">
+        <x:v>110096</x:v>
+      </x:c>
+      <x:c r="D5" s="34" t="str">
+        <x:v>Aiollus</x:v>
+      </x:c>
+      <x:c r="E5" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/110096/aiollus</x:v>
+      </x:c>
+      <x:c r="F5" s="34" t="str"/>
+      <x:c r="G5" s="34" t="str"/>
+      <x:c r="H5" s="34" t="str">
+        <x:v>1657690</x:v>
+      </x:c>
+      <x:c r="I5" s="34" t="str">
+        <x:v>no-image</x:v>
+      </x:c>
+      <x:c r="J5" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K5" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=110096&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L5" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/418826/dark-blood</x:v>
+      </x:c>
+      <x:c r="M5" s="34" t="str">
+        <x:v>418826</x:v>
+      </x:c>
+      <x:c r="N5" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=418826&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O5" s="34" t="str">
+        <x:v>BGG 設計師個人頁使用通用缺圖圖示；BGG 個人相簿查核：圖庫無圖片；相簿來源：https://api.geekdo.com/api/images?ajax=1&amp;gallery=all&amp;nosession=1&amp;objectid=110096&amp;objecttype=person&amp;pageid=1&amp;showcount=10&amp;sort=hot</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="22" customHeight="1">
+      <x:c r="A6" s="34" t="str">
+        <x:v>Alexander Pfister</x:v>
+      </x:c>
+      <x:c r="B6" s="34" t="str">
+        <x:v>alexander pfister</x:v>
+      </x:c>
+      <x:c r="C6" s="34" t="str">
+        <x:v>11767</x:v>
+      </x:c>
+      <x:c r="D6" s="34" t="str">
+        <x:v>Alexander Pfister</x:v>
+      </x:c>
+      <x:c r="E6" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/11767/alexander-pfister</x:v>
+      </x:c>
+      <x:c r="F6" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/BuWLGpEjtxvjUenOYAZyGA__previewthumb/img/nrytzsFnKw4KCcGsa_Mmt7FuDWw=/fit-in/300x320/filters:strip_icc()/pic9706974.jpg</x:v>
+      </x:c>
+      <x:c r="G6" s="34" t="str">
+        <x:v>assets/designers/11767.webp</x:v>
+      </x:c>
+      <x:c r="H6" s="34" t="str">
+        <x:v>9706974</x:v>
+      </x:c>
+      <x:c r="I6" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J6" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K6" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=11767&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L6" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/474125/60deg</x:v>
+      </x:c>
+      <x:c r="M6" s="34" t="str">
+        <x:v>474125</x:v>
+      </x:c>
+      <x:c r="N6" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=474125&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O6" s="34" t="str"/>
+    </x:row>
+    <x:row r="7" ht="22" customHeight="1">
+      <x:c r="A7" s="34" t="str">
+        <x:v>Amy Droz</x:v>
+      </x:c>
+      <x:c r="B7" s="34" t="str">
+        <x:v>amy droz</x:v>
+      </x:c>
+      <x:c r="C7" s="34" t="str">
+        <x:v>151752</x:v>
+      </x:c>
+      <x:c r="D7" s="34" t="str">
+        <x:v>Amy Droz</x:v>
+      </x:c>
+      <x:c r="E7" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/151752/amy-droz</x:v>
+      </x:c>
+      <x:c r="F7" s="34" t="str"/>
+      <x:c r="G7" s="34" t="str"/>
+      <x:c r="H7" s="34" t="str">
+        <x:v>1657690</x:v>
+      </x:c>
+      <x:c r="I7" s="34" t="str">
+        <x:v>no-image</x:v>
+      </x:c>
+      <x:c r="J7" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K7" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=151752&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L7" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/475420/reverie</x:v>
+      </x:c>
+      <x:c r="M7" s="34" t="str">
+        <x:v>475420</x:v>
+      </x:c>
+      <x:c r="N7" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=475420&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O7" s="34" t="str">
+        <x:v>BGG 設計師個人頁使用通用缺圖圖示；BGG 個人相簿查核：圖庫無圖片；相簿來源：https://api.geekdo.com/api/images?ajax=1&amp;gallery=all&amp;nosession=1&amp;objectid=151752&amp;objecttype=person&amp;pageid=1&amp;showcount=10&amp;sort=hot</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="22" customHeight="1">
+      <x:c r="A8" s="34" t="str">
+        <x:v>Andreas Odendahl</x:v>
+      </x:c>
+      <x:c r="B8" s="34" t="str">
+        <x:v>andreas odendahl</x:v>
+      </x:c>
+      <x:c r="C8" s="34" t="str">
+        <x:v>70144</x:v>
+      </x:c>
+      <x:c r="D8" s="34" t="str">
+        <x:v>Andreas Odendahl</x:v>
+      </x:c>
+      <x:c r="E8" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/70144/andreas-odendahl</x:v>
+      </x:c>
+      <x:c r="F8" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/RaFxyT1gnVVaEXBozdj9Gw__previewthumb/img/0EAelpHzTmNWI2ohGnPYIWJX0-I=/fit-in/300x320/filters:strip_icc()/pic8606878.jpg</x:v>
+      </x:c>
+      <x:c r="G8" s="34" t="str">
+        <x:v>assets/designers/70144.webp</x:v>
+      </x:c>
+      <x:c r="H8" s="34" t="str">
+        <x:v>8606878</x:v>
+      </x:c>
+      <x:c r="I8" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J8" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K8" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=70144&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L8" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/471165/northgreen</x:v>
+      </x:c>
+      <x:c r="M8" s="34" t="str">
+        <x:v>471165</x:v>
+      </x:c>
+      <x:c r="N8" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=471165&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O8" s="34" t="str"/>
+    </x:row>
+    <x:row r="9" ht="22" customHeight="1">
+      <x:c r="A9" s="34" t="str">
+        <x:v>Andy Clautice</x:v>
+      </x:c>
+      <x:c r="B9" s="34" t="str">
+        <x:v>andy clautice</x:v>
+      </x:c>
+      <x:c r="C9" s="34" t="str">
+        <x:v>37507</x:v>
+      </x:c>
+      <x:c r="D9" s="34" t="str">
+        <x:v>Andy Clautice</x:v>
+      </x:c>
+      <x:c r="E9" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/37507/andy-clautice</x:v>
+      </x:c>
+      <x:c r="F9" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/ZdNKeoc1PUwGPlV0gVBBVA__previewthumb/img/02zEkJKHl_ne2Ee_eM4JF4PDXac=/fit-in/300x320/filters:strip_icc()/pic8364500.jpg</x:v>
+      </x:c>
+      <x:c r="G9" s="34" t="str">
+        <x:v>assets/designers/37507.webp</x:v>
+      </x:c>
+      <x:c r="H9" s="34" t="str">
+        <x:v>8364500</x:v>
+      </x:c>
+      <x:c r="I9" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J9" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K9" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=37507&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L9" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/426129/dune-imperium-bloodlines</x:v>
+      </x:c>
+      <x:c r="M9" s="34" t="str">
+        <x:v>426129</x:v>
+      </x:c>
+      <x:c r="N9" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=426129&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O9" s="34" t="str"/>
+    </x:row>
+    <x:row r="10" ht="22" customHeight="1">
+      <x:c r="A10" s="34" t="str">
+        <x:v>Antonios Yannopoulos</x:v>
+      </x:c>
+      <x:c r="B10" s="34" t="str">
+        <x:v>antonios yannopoulos</x:v>
+      </x:c>
+      <x:c r="C10" s="34" t="str">
+        <x:v>141462</x:v>
+      </x:c>
+      <x:c r="D10" s="34" t="str">
+        <x:v>Antonios Yannopoulos</x:v>
+      </x:c>
+      <x:c r="E10" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/141462/antonios-yannopoulos</x:v>
+      </x:c>
+      <x:c r="F10" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/zD1q5nX4zzoOhiLeJiTLJA__previewthumb/img/QbD-sG6yEhwTnWT-cbH4jpKl-w0=/fit-in/300x320/filters:strip_icc()/pic7616295.jpg</x:v>
+      </x:c>
+      <x:c r="G10" s="34" t="str">
+        <x:v>assets/designers/141462.webp</x:v>
+      </x:c>
+      <x:c r="H10" s="34" t="str">
+        <x:v>7616295</x:v>
+      </x:c>
+      <x:c r="I10" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J10" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K10" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=141462&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L10" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/448158/vacations-to-greek-islands</x:v>
+      </x:c>
+      <x:c r="M10" s="34" t="str">
+        <x:v>448158</x:v>
+      </x:c>
+      <x:c r="N10" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=448158&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O10" s="34" t="str"/>
+    </x:row>
+    <x:row r="11" ht="22" customHeight="1">
+      <x:c r="A11" s="34" t="str">
+        <x:v>Arve D. Fühler</x:v>
+      </x:c>
+      <x:c r="B11" s="34" t="str">
+        <x:v>arve d. fühler</x:v>
+      </x:c>
+      <x:c r="C11" s="34" t="str">
+        <x:v>72900</x:v>
+      </x:c>
+      <x:c r="D11" s="34" t="str">
+        <x:v>Arve D. Fühler</x:v>
+      </x:c>
+      <x:c r="E11" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/72900/arve-d-fuhler</x:v>
+      </x:c>
+      <x:c r="F11" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/7a3tWGlpbtSxPo8yqV8CIA__previewthumb/img/4plRnI4riLkK6koW5s6OdE5fFEI=/fit-in/300x320/filters:strip_icc()/pic2776518.jpg</x:v>
+      </x:c>
+      <x:c r="G11" s="34" t="str">
+        <x:v>assets/designers/72900.webp</x:v>
+      </x:c>
+      <x:c r="H11" s="34" t="str">
+        <x:v>2776518</x:v>
+      </x:c>
+      <x:c r="I11" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J11" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K11" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=72900&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L11" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/470498/ahrensache</x:v>
+      </x:c>
+      <x:c r="M11" s="34" t="str">
+        <x:v>470498</x:v>
+      </x:c>
+      <x:c r="N11" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=470498&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O11" s="34" t="str"/>
+    </x:row>
+    <x:row r="12" ht="22" customHeight="1">
+      <x:c r="A12" s="34" t="str">
+        <x:v>Attila Szőgyi</x:v>
+      </x:c>
+      <x:c r="B12" s="34" t="str">
+        <x:v>attila szőgyi</x:v>
+      </x:c>
+      <x:c r="C12" s="34" t="str">
+        <x:v>79232</x:v>
+      </x:c>
+      <x:c r="D12" s="34" t="str">
+        <x:v>Attila Szőgyi</x:v>
+      </x:c>
+      <x:c r="E12" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/79232/attila-szogyi</x:v>
+      </x:c>
+      <x:c r="F12" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/7V6JVXyEJ8jgLIt4L_915w__previewthumb/img/7kw_Aml-dKQgt7WMOfbTL1zNmxA=/fit-in/300x320/filters:strip_icc()/pic4748596.png</x:v>
+      </x:c>
+      <x:c r="G12" s="34" t="str">
+        <x:v>assets/designers/79232.webp</x:v>
+      </x:c>
+      <x:c r="H12" s="34" t="str">
+        <x:v>4748596</x:v>
+      </x:c>
+      <x:c r="I12" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J12" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K12" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=79232&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L12" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/234948/prehistory</x:v>
+      </x:c>
+      <x:c r="M12" s="34" t="str">
+        <x:v>234948</x:v>
+      </x:c>
+      <x:c r="N12" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=234948&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O12" s="34" t="str"/>
+    </x:row>
+    <x:row r="13" ht="22" customHeight="1">
+      <x:c r="A13" s="34" t="str">
+        <x:v>Austin Harrison</x:v>
+      </x:c>
+      <x:c r="B13" s="34" t="str">
+        <x:v>austin harrison</x:v>
+      </x:c>
+      <x:c r="C13" s="34" t="str">
+        <x:v>114962</x:v>
+      </x:c>
+      <x:c r="D13" s="34" t="str">
+        <x:v>Austin Harrison</x:v>
+      </x:c>
+      <x:c r="E13" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/114962/austin-harrison</x:v>
+      </x:c>
+      <x:c r="F13" s="34" t="str"/>
+      <x:c r="G13" s="34" t="str"/>
+      <x:c r="H13" s="34" t="str">
+        <x:v>1657690</x:v>
+      </x:c>
+      <x:c r="I13" s="34" t="str">
+        <x:v>no-image</x:v>
+      </x:c>
+      <x:c r="J13" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K13" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=114962&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L13" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/270239/moonrakers</x:v>
+      </x:c>
+      <x:c r="M13" s="34" t="str">
+        <x:v>270239</x:v>
+      </x:c>
+      <x:c r="N13" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=270239&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O13" s="34" t="str">
+        <x:v>BGG 設計師個人頁使用通用缺圖圖示；BGG 個人相簿查核：圖庫無圖片；相簿來源：https://api.geekdo.com/api/images?ajax=1&amp;gallery=all&amp;nosession=1&amp;objectid=114962&amp;objecttype=person&amp;pageid=1&amp;showcount=10&amp;sort=hot</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="22" customHeight="1">
+      <x:c r="A14" s="34" t="str">
+        <x:v>Ayden Lowther</x:v>
+      </x:c>
+      <x:c r="B14" s="34" t="str">
+        <x:v>ayden lowther</x:v>
+      </x:c>
+      <x:c r="C14" s="34" t="str">
+        <x:v>115824</x:v>
+      </x:c>
+      <x:c r="D14" s="34" t="str">
+        <x:v>Ayden Lowther</x:v>
+      </x:c>
+      <x:c r="E14" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/115824/ayden-lowther</x:v>
+      </x:c>
+      <x:c r="F14" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/WP3bRr53YvHpphCd4GjL_w__previewthumb/img/hyTE8qGmHka4CYk8nWc6afG2MbU=/fit-in/300x320/filters:strip_icc()/pic7455279.jpg</x:v>
+      </x:c>
+      <x:c r="G14" s="34" t="str">
+        <x:v>assets/designers/115824.webp</x:v>
+      </x:c>
+      <x:c r="H14" s="34" t="str">
+        <x:v>7455279</x:v>
+      </x:c>
+      <x:c r="I14" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J14" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K14" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=115824&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L14" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/452132/jackpot-set-the-reel-expansions</x:v>
+      </x:c>
+      <x:c r="M14" s="34" t="str">
+        <x:v>452132</x:v>
+      </x:c>
+      <x:c r="N14" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=452132&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O14" s="34" t="str"/>
+    </x:row>
+    <x:row r="15" ht="22" customHeight="1">
+      <x:c r="A15" s="34" t="str">
+        <x:v>Brandon Tibbetts</x:v>
+      </x:c>
+      <x:c r="B15" s="34" t="str">
+        <x:v>brandon tibbetts</x:v>
+      </x:c>
+      <x:c r="C15" s="34" t="str">
+        <x:v>9122</x:v>
+      </x:c>
+      <x:c r="D15" s="34" t="str">
+        <x:v>Brandon Tibbetts</x:v>
+      </x:c>
+      <x:c r="E15" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/9122/brandon-tibbetts</x:v>
+      </x:c>
+      <x:c r="F15" s="34" t="str"/>
+      <x:c r="G15" s="34" t="str"/>
+      <x:c r="H15" s="34" t="str">
+        <x:v>1657690</x:v>
+      </x:c>
+      <x:c r="I15" s="34" t="str">
+        <x:v>no-image</x:v>
+      </x:c>
+      <x:c r="J15" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K15" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=9122&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L15" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/63628/the-manhattan-project</x:v>
+      </x:c>
+      <x:c r="M15" s="34" t="str">
+        <x:v>63628</x:v>
+      </x:c>
+      <x:c r="N15" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=63628&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O15" s="34" t="str">
+        <x:v>BGG 設計師個人頁使用通用缺圖圖示；BGG 個人相簿查核：圖庫未找到可確認人物照片；相簿來源：https://api.geekdo.com/api/images?ajax=1&amp;gallery=all&amp;nosession=1&amp;objectid=9122&amp;objecttype=person&amp;pageid=1&amp;showcount=10&amp;sort=hot</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="22" customHeight="1">
+      <x:c r="A16" s="34" t="str">
+        <x:v>Brendon Cheves</x:v>
+      </x:c>
+      <x:c r="B16" s="34" t="str">
+        <x:v>brendon cheves</x:v>
+      </x:c>
+      <x:c r="C16" s="34" t="str">
+        <x:v>162978</x:v>
+      </x:c>
+      <x:c r="D16" s="34" t="str">
+        <x:v>Brendon Cheves</x:v>
+      </x:c>
+      <x:c r="E16" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/162978/brendon-cheves</x:v>
+      </x:c>
+      <x:c r="F16" s="34" t="str"/>
+      <x:c r="G16" s="34" t="str"/>
+      <x:c r="H16" s="34" t="str">
+        <x:v>1657690</x:v>
+      </x:c>
+      <x:c r="I16" s="34" t="str">
+        <x:v>no-image</x:v>
+      </x:c>
+      <x:c r="J16" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K16" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=162978&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L16" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/439093/red-dog-junction</x:v>
+      </x:c>
+      <x:c r="M16" s="34" t="str">
+        <x:v>439093</x:v>
+      </x:c>
+      <x:c r="N16" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=439093&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O16" s="34" t="str">
+        <x:v>BGG 設計師個人頁使用通用缺圖圖示；BGG 個人相簿查核：圖庫無圖片；相簿來源：https://api.geekdo.com/api/images?ajax=1&amp;gallery=all&amp;nosession=1&amp;objectid=162978&amp;objecttype=person&amp;pageid=1&amp;showcount=10&amp;sort=hot</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="22" customHeight="1">
+      <x:c r="A17" s="34" t="str">
+        <x:v>Brett Sobol</x:v>
+      </x:c>
+      <x:c r="B17" s="34" t="str">
+        <x:v>brett sobol</x:v>
+      </x:c>
+      <x:c r="C17" s="34" t="str">
+        <x:v>76232</x:v>
+      </x:c>
+      <x:c r="D17" s="34" t="str">
+        <x:v>Brett Sobol</x:v>
+      </x:c>
+      <x:c r="E17" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/76232/brett-sobol</x:v>
+      </x:c>
+      <x:c r="F17" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/wp7Qcw-za3aYhLvIyB9Lng__previewthumb/img/BBj4VGTMg4NEIVUf7KlHp4p--MM=/fit-in/300x320/filters:strip_icc()/pic2196364.jpg</x:v>
+      </x:c>
+      <x:c r="G17" s="34" t="str">
+        <x:v>assets/designers/76232.webp</x:v>
+      </x:c>
+      <x:c r="H17" s="34" t="str">
+        <x:v>2196364</x:v>
+      </x:c>
+      <x:c r="I17" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J17" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K17" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=76232&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L17" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/208024/reckoners</x:v>
+      </x:c>
+      <x:c r="M17" s="34" t="str">
+        <x:v>208024</x:v>
+      </x:c>
+      <x:c r="N17" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=208024&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O17" s="34" t="str"/>
+    </x:row>
+    <x:row r="18" ht="22" customHeight="1">
+      <x:c r="A18" s="34" t="str">
+        <x:v>Brian Lewis</x:v>
+      </x:c>
+      <x:c r="B18" s="34" t="str">
+        <x:v>brian lewis</x:v>
+      </x:c>
+      <x:c r="C18" s="34" t="str">
+        <x:v>58135</x:v>
+      </x:c>
+      <x:c r="D18" s="34" t="str">
+        <x:v>Brian Lewis</x:v>
+      </x:c>
+      <x:c r="E18" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/58135/brian-lewis</x:v>
+      </x:c>
+      <x:c r="F18" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/4f3jitKluASc-pe2JrCVgg__previewthumb/img/0CTXKsdHO9ZnSXyWfEMSVAv6Q0Y=/fit-in/300x320/filters:strip_icc()/pic4992345.jpg</x:v>
+      </x:c>
+      <x:c r="G18" s="34" t="str">
+        <x:v>assets/designers/58135.webp</x:v>
+      </x:c>
+      <x:c r="H18" s="34" t="str">
+        <x:v>4992345</x:v>
+      </x:c>
+      <x:c r="I18" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J18" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K18" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=58135&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L18" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/318009/dinosaur-island-rawr-n-write</x:v>
+      </x:c>
+      <x:c r="M18" s="34" t="str">
+        <x:v>318009</x:v>
+      </x:c>
+      <x:c r="N18" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=318009&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O18" s="34" t="str"/>
+    </x:row>
+    <x:row r="19" ht="22" customHeight="1">
+      <x:c r="A19" s="34" t="str">
+        <x:v>Bryan Burgoyne</x:v>
+      </x:c>
+      <x:c r="B19" s="34" t="str">
+        <x:v>bryan burgoyne</x:v>
+      </x:c>
+      <x:c r="C19" s="34" t="str">
+        <x:v>124157</x:v>
+      </x:c>
+      <x:c r="D19" s="34" t="str">
+        <x:v>Bryan Burgoyne</x:v>
+      </x:c>
+      <x:c r="E19" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/124157/bryan-burgoyne</x:v>
+      </x:c>
+      <x:c r="F19" s="34" t="str"/>
+      <x:c r="G19" s="34" t="str"/>
+      <x:c r="H19" s="34" t="str">
+        <x:v>1657690</x:v>
+      </x:c>
+      <x:c r="I19" s="34" t="str">
+        <x:v>no-image</x:v>
+      </x:c>
+      <x:c r="J19" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K19" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=124157&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L19" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/406660/seaside</x:v>
+      </x:c>
+      <x:c r="M19" s="34" t="str">
+        <x:v>406660</x:v>
+      </x:c>
+      <x:c r="N19" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=406660&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O19" s="34" t="str">
+        <x:v>BGG 設計師個人頁使用通用缺圖圖示；BGG 個人相簿查核：圖庫無圖片；相簿來源：https://api.geekdo.com/api/images?ajax=1&amp;gallery=all&amp;nosession=1&amp;objectid=124157&amp;objecttype=person&amp;pageid=1&amp;showcount=10&amp;sort=hot</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="22" customHeight="1">
+      <x:c r="A20" s="34" t="str">
+        <x:v>Bryan Kline</x:v>
+      </x:c>
+      <x:c r="B20" s="34" t="str">
+        <x:v>bryan kline</x:v>
+      </x:c>
+      <x:c r="C20" s="34" t="str">
+        <x:v>91972</x:v>
+      </x:c>
+      <x:c r="D20" s="34" t="str">
+        <x:v>Bryan Kline</x:v>
+      </x:c>
+      <x:c r="E20" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/91972/bryan-kline</x:v>
+      </x:c>
+      <x:c r="F20" s="34" t="str"/>
+      <x:c r="G20" s="34" t="str"/>
+      <x:c r="H20" s="34" t="str">
+        <x:v>1657690</x:v>
+      </x:c>
+      <x:c r="I20" s="34" t="str">
+        <x:v>no-image</x:v>
+      </x:c>
+      <x:c r="J20" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K20" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=91972&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L20" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/396914/stellar-drift-pull-and-write</x:v>
+      </x:c>
+      <x:c r="M20" s="34" t="str">
+        <x:v>396914</x:v>
+      </x:c>
+      <x:c r="N20" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=396914&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O20" s="34" t="str">
+        <x:v>BGG 設計師個人頁使用通用缺圖圖示；BGG 個人相簿查核：圖庫無圖片；相簿來源：https://api.geekdo.com/api/images?ajax=1&amp;gallery=all&amp;nosession=1&amp;objectid=91972&amp;objecttype=person&amp;pageid=1&amp;showcount=10&amp;sort=hot</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="22" customHeight="1">
+      <x:c r="A21" s="34" t="str">
+        <x:v>Caleb Vance</x:v>
+      </x:c>
+      <x:c r="B21" s="34" t="str">
+        <x:v>caleb vance</x:v>
+      </x:c>
+      <x:c r="C21" s="34" t="str">
+        <x:v>163468</x:v>
+      </x:c>
+      <x:c r="D21" s="34" t="str">
+        <x:v>Caleb Vance</x:v>
+      </x:c>
+      <x:c r="E21" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/163468/caleb-vance</x:v>
+      </x:c>
+      <x:c r="F21" s="34" t="str"/>
+      <x:c r="G21" s="34" t="str"/>
+      <x:c r="H21" s="34" t="str">
+        <x:v>1657690</x:v>
+      </x:c>
+      <x:c r="I21" s="34" t="str">
+        <x:v>no-image</x:v>
+      </x:c>
+      <x:c r="J21" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K21" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=163468&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L21" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/426129/dune-imperium-bloodlines</x:v>
+      </x:c>
+      <x:c r="M21" s="34" t="str">
+        <x:v>426129</x:v>
+      </x:c>
+      <x:c r="N21" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=426129&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O21" s="34" t="str">
+        <x:v>BGG 設計師個人頁使用通用缺圖圖示；BGG 個人相簿查核：圖庫無圖片；相簿來源：https://api.geekdo.com/api/images?ajax=1&amp;gallery=all&amp;nosession=1&amp;objectid=163468&amp;objecttype=person&amp;pageid=1&amp;showcount=10&amp;sort=hot</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="22" customHeight="1">
+      <x:c r="A22" s="34" t="str">
+        <x:v>Christophe Boelinger</x:v>
+      </x:c>
+      <x:c r="B22" s="34" t="str">
+        <x:v>christophe boelinger</x:v>
+      </x:c>
+      <x:c r="C22" s="34" t="str">
+        <x:v>1206</x:v>
+      </x:c>
+      <x:c r="D22" s="34" t="str">
+        <x:v>Christophe Boelinger</x:v>
+      </x:c>
+      <x:c r="E22" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/1206/christophe-boelinger</x:v>
+      </x:c>
+      <x:c r="F22" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/bWPDJrn6R2tR2xutnIXzrg__previewthumb/img/7V_bIT0r5gZrC4K7FDSUQ6vWEVk=/fit-in/300x320/filters:strip_icc()/pic464079.jpg</x:v>
+      </x:c>
+      <x:c r="G22" s="34" t="str">
+        <x:v>assets/designers/1206.webp</x:v>
+      </x:c>
+      <x:c r="H22" s="34" t="str">
+        <x:v>464079</x:v>
+      </x:c>
+      <x:c r="I22" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J22" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K22" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=1206&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L22" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/154863/archipelago-war-and-peace</x:v>
+      </x:c>
+      <x:c r="M22" s="34" t="str">
+        <x:v>154863</x:v>
+      </x:c>
+      <x:c r="N22" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=154863&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O22" s="34" t="str"/>
+    </x:row>
+    <x:row r="23" ht="22" customHeight="1">
+      <x:c r="A23" s="34" t="str">
+        <x:v>Cody Miller</x:v>
+      </x:c>
+      <x:c r="B23" s="34" t="str">
+        <x:v>cody miller</x:v>
+      </x:c>
+      <x:c r="C23" s="34" t="str">
+        <x:v>42141</x:v>
+      </x:c>
+      <x:c r="D23" s="34" t="str">
+        <x:v>Cody Miller</x:v>
+      </x:c>
+      <x:c r="E23" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/42141/cody-miller</x:v>
+      </x:c>
+      <x:c r="F23" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/-46og34gBa5YG9_3qDhe3g__previewthumb/img/8cmfUvssO7qxQ73QXEg_AaKkOz4=/fit-in/300x320/filters:strip_icc()/pic2257838.jpg</x:v>
+      </x:c>
+      <x:c r="G23" s="34" t="str">
+        <x:v>assets/designers/42141.webp</x:v>
+      </x:c>
+      <x:c r="H23" s="34" t="str">
+        <x:v>2257838</x:v>
+      </x:c>
+      <x:c r="I23" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J23" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K23" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=42141&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L23" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/82222/xia-legends-of-a-drift-system</x:v>
+      </x:c>
+      <x:c r="M23" s="34" t="str">
+        <x:v>82222</x:v>
+      </x:c>
+      <x:c r="N23" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=82222&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O23" s="34" t="str"/>
+    </x:row>
+    <x:row r="24" ht="22" customHeight="1">
+      <x:c r="A24" s="34" t="str">
+        <x:v>Cole Wehrle</x:v>
+      </x:c>
+      <x:c r="B24" s="34" t="str">
+        <x:v>cole wehrle</x:v>
+      </x:c>
+      <x:c r="C24" s="34" t="str">
+        <x:v>35585</x:v>
+      </x:c>
+      <x:c r="D24" s="34" t="str">
+        <x:v>Cole Wehrle</x:v>
+      </x:c>
+      <x:c r="E24" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/35585/cole-wehrle</x:v>
+      </x:c>
+      <x:c r="F24" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/CzQxR5ClA4720FRCmZyrKg__previewthumb/img/KgNLVyQqr_MgjIF1ojb3ICeVjUo=/fit-in/300x320/filters:strip_icc()/pic4136195.jpg</x:v>
+      </x:c>
+      <x:c r="G24" s="34" t="str">
+        <x:v>assets/designers/35585.webp</x:v>
+      </x:c>
+      <x:c r="H24" s="34" t="str">
+        <x:v>4136195</x:v>
+      </x:c>
+      <x:c r="I24" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J24" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K24" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=35585&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L24" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/349750/molly-house</x:v>
+      </x:c>
+      <x:c r="M24" s="34" t="str">
+        <x:v>349750</x:v>
+      </x:c>
+      <x:c r="N24" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=349750&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O24" s="34" t="str"/>
+    </x:row>
+    <x:row r="25" ht="22" customHeight="1">
+      <x:c r="A25" s="34" t="str">
+        <x:v>Corey Konieczka</x:v>
+      </x:c>
+      <x:c r="B25" s="34" t="str">
+        <x:v>corey konieczka</x:v>
+      </x:c>
+      <x:c r="C25" s="34" t="str">
+        <x:v>6651</x:v>
+      </x:c>
+      <x:c r="D25" s="34" t="str">
+        <x:v>Corey Konieczka</x:v>
+      </x:c>
+      <x:c r="E25" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/6651/corey-konieczka</x:v>
+      </x:c>
+      <x:c r="F25" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/C0-6A8zrSGxGJPBVDwHwEQ__previewthumb/img/x_otnbhoJmPu86ZcEqFYPJ-vkXQ=/fit-in/300x320/filters:strip_icc()/pic8337728.jpg</x:v>
+      </x:c>
+      <x:c r="G25" s="34" t="str">
+        <x:v>assets/designers/6651.webp</x:v>
+      </x:c>
+      <x:c r="H25" s="34" t="str">
+        <x:v>8337728</x:v>
+      </x:c>
+      <x:c r="I25" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J25" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K25" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=6651&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L25" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/175155/forbidden-stars</x:v>
+      </x:c>
+      <x:c r="M25" s="34" t="str">
+        <x:v>175155</x:v>
+      </x:c>
+      <x:c r="N25" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=175155&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O25" s="34" t="str"/>
+    </x:row>
+    <x:row r="26" ht="22" customHeight="1">
+      <x:c r="A26" s="34" t="str">
+        <x:v>Dan Germain</x:v>
+      </x:c>
+      <x:c r="B26" s="34" t="str">
+        <x:v>dan germain</x:v>
+      </x:c>
+      <x:c r="C26" s="34" t="str">
+        <x:v>110089</x:v>
+      </x:c>
+      <x:c r="D26" s="34" t="str">
+        <x:v>Dan Germain</x:v>
+      </x:c>
+      <x:c r="E26" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/110089/dan-germain</x:v>
+      </x:c>
+      <x:c r="F26" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/87uKlUcVAPPJmxndZRuVvQ__previewthumb/img/QXXh2dZz1nWptfYRhj6jY8EinOg=/fit-in/300x320/filters:strip_icc()/pic6963344.jpg</x:v>
+      </x:c>
+      <x:c r="G26" s="34" t="str">
+        <x:v>assets/designers/110089.webp</x:v>
+      </x:c>
+      <x:c r="H26" s="34" t="str">
+        <x:v>6963344</x:v>
+      </x:c>
+      <x:c r="I26" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J26" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K26" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=110089&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L26" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/479457/braided-skies</x:v>
+      </x:c>
+      <x:c r="M26" s="34" t="str">
+        <x:v>479457</x:v>
+      </x:c>
+      <x:c r="N26" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=479457&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O26" s="34" t="str"/>
+    </x:row>
+    <x:row r="27" ht="22" customHeight="1">
+      <x:c r="A27" s="34" t="str">
+        <x:v>Dani Garcia</x:v>
+      </x:c>
+      <x:c r="B27" s="34" t="str">
+        <x:v>dani garcia</x:v>
+      </x:c>
+      <x:c r="C27" s="34" t="str">
+        <x:v>117012</x:v>
+      </x:c>
+      <x:c r="D27" s="34" t="str">
+        <x:v>Dani Garcia</x:v>
+      </x:c>
+      <x:c r="E27" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/117012/dani-garcia</x:v>
+      </x:c>
+      <x:c r="F27" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/sKMb4zCzXaPzmFycGOyD6w__large/img/opJNMmAqZNQcGiL3TTfrbZQlWZc=/fit-in/1024x1024/filters:no_upscale():strip_icc()/pic9848226.jpg</x:v>
+      </x:c>
+      <x:c r="G27" s="34" t="str">
+        <x:v>assets/designers/117012.webp</x:v>
+      </x:c>
+      <x:c r="H27" s="34" t="str">
+        <x:v>9848226</x:v>
+      </x:c>
+      <x:c r="I27" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J27" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K27" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=117012&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L27" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/469504/diables</x:v>
+      </x:c>
+      <x:c r="M27" s="34" t="str">
+        <x:v>469504</x:v>
+      </x:c>
+      <x:c r="N27" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=469504&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O27" s="34" t="str">
+        <x:v>BGG 主要圖片為 W3D 立方標誌，未提供人物照片；已目視確認 BGG 個人相簿人物照片／個人頭像；圖片說明：The Voynich Puzzle；相簿查核：https://api.geekdo.com/api/images?ajax=1&amp;gallery=all&amp;nosession=1&amp;objectid=117012&amp;objecttype=person&amp;pageid=1&amp;showcount=10&amp;sort=hot；圖片頁：https://boardgamegeek.com/image/9848226/the-voynich-puzzle</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="22" customHeight="1">
+      <x:c r="A28" s="34" t="str">
+        <x:v>Daniel Galbraith</x:v>
+      </x:c>
+      <x:c r="B28" s="34" t="str">
+        <x:v>daniel galbraith</x:v>
+      </x:c>
+      <x:c r="C28" s="34" t="str">
+        <x:v>171224</x:v>
+      </x:c>
+      <x:c r="D28" s="34" t="str">
+        <x:v>Daniel Galbraith</x:v>
+      </x:c>
+      <x:c r="E28" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/171224/daniel-galbraith</x:v>
+      </x:c>
+      <x:c r="F28" s="34" t="str"/>
+      <x:c r="G28" s="34" t="str"/>
+      <x:c r="H28" s="34" t="str">
+        <x:v>1657690</x:v>
+      </x:c>
+      <x:c r="I28" s="34" t="str">
+        <x:v>no-image</x:v>
+      </x:c>
+      <x:c r="J28" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K28" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=171224&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L28" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/455519/isle-of-feathers</x:v>
+      </x:c>
+      <x:c r="M28" s="34" t="str">
+        <x:v>455519</x:v>
+      </x:c>
+      <x:c r="N28" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=455519&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O28" s="34" t="str">
+        <x:v>BGG 設計師個人頁使用通用缺圖圖示；BGG 個人相簿查核：圖庫無圖片；相簿來源：https://api.geekdo.com/api/images?ajax=1&amp;gallery=all&amp;nosession=1&amp;objectid=171224&amp;objecttype=person&amp;pageid=1&amp;showcount=10&amp;sort=hot</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="22" customHeight="1">
+      <x:c r="A29" s="34" t="str">
+        <x:v>Danilo Sabia</x:v>
+      </x:c>
+      <x:c r="B29" s="34" t="str">
+        <x:v>danilo sabia</x:v>
+      </x:c>
+      <x:c r="C29" s="34" t="str">
+        <x:v>101481</x:v>
+      </x:c>
+      <x:c r="D29" s="34" t="str">
+        <x:v>Danilo Sabia</x:v>
+      </x:c>
+      <x:c r="E29" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/101481/danilo-sabia</x:v>
+      </x:c>
+      <x:c r="F29" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/hVk_YFJA1GX5jtdHsl4JHg__previewthumb/img/Puo0uD9ZWNqfaqn7Pcp_DlUtQsU=/fit-in/300x320/filters:strip_icc()/pic3602917.jpg</x:v>
+      </x:c>
+      <x:c r="G29" s="34" t="str">
+        <x:v>assets/designers/101481.webp</x:v>
+      </x:c>
+      <x:c r="H29" s="34" t="str">
+        <x:v>3602917</x:v>
+      </x:c>
+      <x:c r="I29" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J29" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K29" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=101481&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L29" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/468569/tatanka</x:v>
+      </x:c>
+      <x:c r="M29" s="34" t="str">
+        <x:v>468569</x:v>
+      </x:c>
+      <x:c r="N29" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=468569&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O29" s="34" t="str"/>
+    </x:row>
+    <x:row r="30" ht="22" customHeight="1">
+      <x:c r="A30" s="34" t="str">
+        <x:v>Dariusz Mindur</x:v>
+      </x:c>
+      <x:c r="B30" s="34" t="str">
+        <x:v>dariusz mindur</x:v>
+      </x:c>
+      <x:c r="C30" s="34" t="str">
+        <x:v>169366</x:v>
+      </x:c>
+      <x:c r="D30" s="34" t="str">
+        <x:v>Dariusz Mindur</x:v>
+      </x:c>
+      <x:c r="E30" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/169366/dariusz-mindur</x:v>
+      </x:c>
+      <x:c r="F30" s="34" t="str"/>
+      <x:c r="G30" s="34" t="str"/>
+      <x:c r="H30" s="34" t="str">
+        <x:v>1657690</x:v>
+      </x:c>
+      <x:c r="I30" s="34" t="str">
+        <x:v>no-image</x:v>
+      </x:c>
+      <x:c r="J30" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K30" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=169366&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L30" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/448859/borealis-arctic-expeditions-society-for-polar-inqu</x:v>
+      </x:c>
+      <x:c r="M30" s="34" t="str">
+        <x:v>448859</x:v>
+      </x:c>
+      <x:c r="N30" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=448859&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O30" s="34" t="str">
+        <x:v>BGG 設計師個人頁使用通用缺圖圖示；BGG 個人相簿查核：圖庫無圖片；相簿來源：https://api.geekdo.com/api/images?ajax=1&amp;gallery=all&amp;nosession=1&amp;objectid=169366&amp;objecttype=person&amp;pageid=1&amp;showcount=10&amp;sort=hot</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="22" customHeight="1">
+      <x:c r="A31" s="34" t="str">
+        <x:v>Daryl Andrews</x:v>
+      </x:c>
+      <x:c r="B31" s="34" t="str">
+        <x:v>daryl andrews</x:v>
+      </x:c>
+      <x:c r="C31" s="34" t="str">
+        <x:v>67502</x:v>
+      </x:c>
+      <x:c r="D31" s="34" t="str">
+        <x:v>Daryl Andrews</x:v>
+      </x:c>
+      <x:c r="E31" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/67502/daryl-andrews</x:v>
+      </x:c>
+      <x:c r="F31" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/Ot2Ah-gk81kcTXDXQN0BMQ__previewthumb/img/cg1W26fhjoFjqmGkXtOKLzGJMDY=/fit-in/300x320/filters:strip_icc()/pic1601662.jpg</x:v>
+      </x:c>
+      <x:c r="G31" s="34" t="str">
+        <x:v>assets/designers/67502.webp</x:v>
+      </x:c>
+      <x:c r="H31" s="34" t="str">
+        <x:v>1601662</x:v>
+      </x:c>
+      <x:c r="I31" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J31" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K31" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=67502&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L31" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/466710</x:v>
+      </x:c>
+      <x:c r="M31" s="34" t="str">
+        <x:v>466710</x:v>
+      </x:c>
+      <x:c r="N31" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=466710&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O31" s="34" t="str"/>
+    </x:row>
+    <x:row r="32" ht="22" customHeight="1">
+      <x:c r="A32" s="34" t="str">
+        <x:v>David Goh</x:v>
+      </x:c>
+      <x:c r="B32" s="34" t="str">
+        <x:v>david goh</x:v>
+      </x:c>
+      <x:c r="C32" s="34" t="str">
+        <x:v>85703</x:v>
+      </x:c>
+      <x:c r="D32" s="34" t="str">
+        <x:v>David Goh</x:v>
+      </x:c>
+      <x:c r="E32" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/85703/david-goh</x:v>
+      </x:c>
+      <x:c r="F32" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/u7AS-du5KiLPRH4rWMj5PA__previewthumb/img/iBCI-Ihp20Rx_XJZXx9e6aPmbNE=/fit-in/300x320/filters:strip_icc()/pic9847610.jpg</x:v>
+      </x:c>
+      <x:c r="G32" s="34" t="str">
+        <x:v>assets/designers/85703.webp</x:v>
+      </x:c>
+      <x:c r="H32" s="34" t="str">
+        <x:v>9847610</x:v>
+      </x:c>
+      <x:c r="I32" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J32" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K32" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=85703&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L32" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/317940/mercurial</x:v>
+      </x:c>
+      <x:c r="M32" s="34" t="str">
+        <x:v>317940</x:v>
+      </x:c>
+      <x:c r="N32" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=317940&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O32" s="34" t="str"/>
+    </x:row>
+    <x:row r="33" ht="22" customHeight="1">
+      <x:c r="A33" s="34" t="str">
+        <x:v>David McGregor</x:v>
+      </x:c>
+      <x:c r="B33" s="34" t="str">
+        <x:v>david mcgregor</x:v>
+      </x:c>
+      <x:c r="C33" s="34" t="str">
+        <x:v>105446</x:v>
+      </x:c>
+      <x:c r="D33" s="34" t="str">
+        <x:v>David McGregor</x:v>
+      </x:c>
+      <x:c r="E33" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/105446/david-mcgregor</x:v>
+      </x:c>
+      <x:c r="F33" s="34" t="str"/>
+      <x:c r="G33" s="34" t="str"/>
+      <x:c r="H33" s="34" t="str">
+        <x:v>1657690</x:v>
+      </x:c>
+      <x:c r="I33" s="34" t="str">
+        <x:v>no-image</x:v>
+      </x:c>
+      <x:c r="J33" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K33" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=105446&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L33" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/318009/dinosaur-island-rawr-n-write</x:v>
+      </x:c>
+      <x:c r="M33" s="34" t="str">
+        <x:v>318009</x:v>
+      </x:c>
+      <x:c r="N33" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=318009&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O33" s="34" t="str">
+        <x:v>BGG 設計師個人頁使用通用缺圖圖示；BGG 個人相簿查核：圖庫無圖片；相簿來源：https://api.geekdo.com/api/images?ajax=1&amp;gallery=all&amp;nosession=1&amp;objectid=105446&amp;objecttype=person&amp;pageid=1&amp;showcount=10&amp;sort=hot</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="22" customHeight="1">
+      <x:c r="A34" s="34" t="str">
+        <x:v>Dennis K. Chan</x:v>
+      </x:c>
+      <x:c r="B34" s="34" t="str">
+        <x:v>dennis k. chan</x:v>
+      </x:c>
+      <x:c r="C34" s="34" t="str">
+        <x:v>129749</x:v>
+      </x:c>
+      <x:c r="D34" s="34" t="str">
+        <x:v>Dennis K. Chan</x:v>
+      </x:c>
+      <x:c r="E34" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/129749/dennis-k-chan</x:v>
+      </x:c>
+      <x:c r="F34" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/R-z2zsd5cwMLOC2xQSFIfA__previewthumb/img/xLbjDnk8-XWm3P206ZxBl2Zrgjw=/fit-in/300x320/filters:strip_icc()/pic5619811.jpg</x:v>
+      </x:c>
+      <x:c r="G34" s="34" t="str">
+        <x:v>assets/designers/129749.webp</x:v>
+      </x:c>
+      <x:c r="H34" s="34" t="str">
+        <x:v>5619811</x:v>
+      </x:c>
+      <x:c r="I34" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J34" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K34" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=129749&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L34" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/378291/beyond-the-sun-leaders-of-the-new-dawn</x:v>
+      </x:c>
+      <x:c r="M34" s="34" t="str">
+        <x:v>378291</x:v>
+      </x:c>
+      <x:c r="N34" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=378291&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O34" s="34" t="str"/>
+    </x:row>
+    <x:row r="35" ht="22" customHeight="1">
+      <x:c r="A35" s="34" t="str">
+        <x:v>Dennis Northcott</x:v>
+      </x:c>
+      <x:c r="B35" s="34" t="str">
+        <x:v>dennis northcott</x:v>
+      </x:c>
+      <x:c r="C35" s="34" t="str">
+        <x:v>154241</x:v>
+      </x:c>
+      <x:c r="D35" s="34" t="str">
+        <x:v>Dennis Northcott</x:v>
+      </x:c>
+      <x:c r="E35" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/154241/dennis-northcott</x:v>
+      </x:c>
+      <x:c r="F35" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/tPYjok5g86-vq5Ta2mSmzQ__previewthumb/img/YIG88UKfZ-Y_qlwbZA5cYMjXH_w=/fit-in/300x320/filters:strip_icc()/pic7565498.jpg</x:v>
+      </x:c>
+      <x:c r="G35" s="34" t="str">
+        <x:v>assets/designers/154241.webp</x:v>
+      </x:c>
+      <x:c r="H35" s="34" t="str">
+        <x:v>7565498</x:v>
+      </x:c>
+      <x:c r="I35" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J35" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K35" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=154241&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L35" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/470410/galactic-cruise-perfect-planning-promo-card</x:v>
+      </x:c>
+      <x:c r="M35" s="34" t="str">
+        <x:v>470410</x:v>
+      </x:c>
+      <x:c r="N35" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=470410&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O35" s="34" t="str"/>
+    </x:row>
+    <x:row r="36" ht="22" customHeight="1">
+      <x:c r="A36" s="34" t="str">
+        <x:v>Donald X. Vaccarino</x:v>
+      </x:c>
+      <x:c r="B36" s="34" t="str">
+        <x:v>donald x. vaccarino</x:v>
+      </x:c>
+      <x:c r="C36" s="34" t="str">
+        <x:v>10525</x:v>
+      </x:c>
+      <x:c r="D36" s="34" t="str">
+        <x:v>Donald X. Vaccarino</x:v>
+      </x:c>
+      <x:c r="E36" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/10525/donald-x-vaccarino</x:v>
+      </x:c>
+      <x:c r="F36" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/tQn_X6iGjaXAKSl9mMQC5w__previewthumb/img/ThOEqjBApJRVaT3mUwYmdSKvDgQ=/fit-in/300x320/filters:strip_icc()/pic5294806.jpg</x:v>
+      </x:c>
+      <x:c r="G36" s="34" t="str">
+        <x:v>assets/designers/10525.webp</x:v>
+      </x:c>
+      <x:c r="H36" s="34" t="str">
+        <x:v>5294806</x:v>
+      </x:c>
+      <x:c r="I36" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J36" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K36" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=10525&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L36" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/478591/moon-colony-bloodbath-aliens-from-space</x:v>
+      </x:c>
+      <x:c r="M36" s="34" t="str">
+        <x:v>478591</x:v>
+      </x:c>
+      <x:c r="N36" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=478591&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O36" s="34" t="str"/>
+    </x:row>
+    <x:row r="37" ht="22" customHeight="1">
+      <x:c r="A37" s="34" t="str">
+        <x:v>Dusty Droz</x:v>
+      </x:c>
+      <x:c r="B37" s="34" t="str">
+        <x:v>dusty droz</x:v>
+      </x:c>
+      <x:c r="C37" s="34" t="str">
+        <x:v>151753</x:v>
+      </x:c>
+      <x:c r="D37" s="34" t="str">
+        <x:v>Dusty Droz</x:v>
+      </x:c>
+      <x:c r="E37" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/151753/dusty-droz</x:v>
+      </x:c>
+      <x:c r="F37" s="34" t="str"/>
+      <x:c r="G37" s="34" t="str"/>
+      <x:c r="H37" s="34" t="str">
+        <x:v>1657690</x:v>
+      </x:c>
+      <x:c r="I37" s="34" t="str">
+        <x:v>no-image</x:v>
+      </x:c>
+      <x:c r="J37" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K37" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=151753&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L37" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/475420/reverie</x:v>
+      </x:c>
+      <x:c r="M37" s="34" t="str">
+        <x:v>475420</x:v>
+      </x:c>
+      <x:c r="N37" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=475420&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O37" s="34" t="str">
+        <x:v>BGG 設計師個人頁使用通用缺圖圖示；BGG 個人相簿查核：圖庫無圖片；相簿來源：https://api.geekdo.com/api/images?ajax=1&amp;gallery=all&amp;nosession=1&amp;objectid=151753&amp;objecttype=person&amp;pageid=1&amp;showcount=10&amp;sort=hot</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="22" customHeight="1">
+      <x:c r="A38" s="34" t="str">
+        <x:v>Dávid Turczi</x:v>
+      </x:c>
+      <x:c r="B38" s="34" t="str">
+        <x:v>dávid turczi</x:v>
+      </x:c>
+      <x:c r="C38" s="34" t="str">
+        <x:v>76227</x:v>
+      </x:c>
+      <x:c r="D38" s="34" t="str">
+        <x:v>Dávid Turczi</x:v>
+      </x:c>
+      <x:c r="E38" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/76227/david-turczi</x:v>
+      </x:c>
+      <x:c r="F38" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/tSUT-8gABUmkfJfyjQHIKg__previewthumb/img/1BUKwbd_vJ0IROSdeAsM8vULRhA=/fit-in/300x320/filters:strip_icc()/pic8338071.jpg</x:v>
+      </x:c>
+      <x:c r="G38" s="34" t="str">
+        <x:v>assets/designers/76227.webp</x:v>
+      </x:c>
+      <x:c r="H38" s="34" t="str">
+        <x:v>8338071</x:v>
+      </x:c>
+      <x:c r="I38" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J38" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K38" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=76227&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L38" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/292126/excavation-earth</x:v>
+      </x:c>
+      <x:c r="M38" s="34" t="str">
+        <x:v>292126</x:v>
+      </x:c>
+      <x:c r="N38" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=292126&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O38" s="34" t="str"/>
+    </x:row>
+    <x:row r="39" ht="22" customHeight="1">
+      <x:c r="A39" s="34" t="str">
+        <x:v>Egidio Trambaiolli Neto</x:v>
+      </x:c>
+      <x:c r="B39" s="34" t="str">
+        <x:v>egidio trambaiolli neto</x:v>
+      </x:c>
+      <x:c r="C39" s="34" t="str">
+        <x:v>157121</x:v>
+      </x:c>
+      <x:c r="D39" s="34" t="str">
+        <x:v>Egidio Trambaiolli Neto</x:v>
+      </x:c>
+      <x:c r="E39" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/157121/egidio-trambaiolli-neto</x:v>
+      </x:c>
+      <x:c r="F39" s="34" t="str"/>
+      <x:c r="G39" s="34" t="str"/>
+      <x:c r="H39" s="34" t="str">
+        <x:v>1657690</x:v>
+      </x:c>
+      <x:c r="I39" s="34" t="str">
+        <x:v>no-image</x:v>
+      </x:c>
+      <x:c r="J39" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K39" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=157121&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L39" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/403434/excalibur</x:v>
+      </x:c>
+      <x:c r="M39" s="34" t="str">
+        <x:v>403434</x:v>
+      </x:c>
+      <x:c r="N39" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=403434&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O39" s="34" t="str">
+        <x:v>BGG 設計師個人頁使用通用缺圖圖示；BGG 個人相簿查核：圖庫無圖片；相簿來源：https://api.geekdo.com/api/images?ajax=1&amp;gallery=all&amp;nosession=1&amp;objectid=157121&amp;objecttype=person&amp;pageid=1&amp;showcount=10&amp;sort=hot</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="22" customHeight="1">
+      <x:c r="A40" s="34" t="str">
+        <x:v>Eilif Svensson</x:v>
+      </x:c>
+      <x:c r="B40" s="34" t="str">
+        <x:v>eilif svensson</x:v>
+      </x:c>
+      <x:c r="C40" s="34" t="str">
+        <x:v>9637</x:v>
+      </x:c>
+      <x:c r="D40" s="34" t="str">
+        <x:v>Eilif Svensson</x:v>
+      </x:c>
+      <x:c r="E40" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/9637/eilif-svensson</x:v>
+      </x:c>
+      <x:c r="F40" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/zRvP_RTPQG3zkSxTzNax9g__previewthumb/img/1_X2dbgWNM0D0FarV5FsRE3WwPk=/fit-in/300x320/filters:strip_icc()/pic2221935.jpg</x:v>
+      </x:c>
+      <x:c r="G40" s="34" t="str">
+        <x:v>assets/designers/9637.webp</x:v>
+      </x:c>
+      <x:c r="H40" s="34" t="str">
+        <x:v>2221935</x:v>
+      </x:c>
+      <x:c r="I40" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J40" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K40" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=9637&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L40" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/461255/wild-world</x:v>
+      </x:c>
+      <x:c r="M40" s="34" t="str">
+        <x:v>461255</x:v>
+      </x:c>
+      <x:c r="N40" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=461255&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O40" s="34" t="str"/>
+    </x:row>
+    <x:row r="41" ht="22" customHeight="1">
+      <x:c r="A41" s="34" t="str">
+        <x:v>Elwen</x:v>
+      </x:c>
+      <x:c r="B41" s="34" t="str">
+        <x:v>elwen</x:v>
+      </x:c>
+      <x:c r="C41" s="34" t="str">
+        <x:v>127823</x:v>
+      </x:c>
+      <x:c r="D41" s="34" t="str">
+        <x:v>Elwen</x:v>
+      </x:c>
+      <x:c r="E41" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/127823/elwen</x:v>
+      </x:c>
+      <x:c r="F41" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/dzR5IZ5IeKriWn0XJOj_eg__previewthumb/img/huYNmhV5KPbx6wR9FvuqCR1b6UQ=/fit-in/300x320/filters:strip_icc()/pic6452692.jpg</x:v>
+      </x:c>
+      <x:c r="G41" s="34" t="str">
+        <x:v>assets/designers/127823.webp</x:v>
+      </x:c>
+      <x:c r="H41" s="34" t="str">
+        <x:v>6452692</x:v>
+      </x:c>
+      <x:c r="I41" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J41" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K41" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=127823&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L41" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/475207/lost-ruins-of-arnak-surprise-shipment</x:v>
+      </x:c>
+      <x:c r="M41" s="34" t="str">
+        <x:v>475207</x:v>
+      </x:c>
+      <x:c r="N41" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=475207&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O41" s="34" t="str"/>
+    </x:row>
+    <x:row r="42" ht="22" customHeight="1">
+      <x:c r="A42" s="34" t="str">
+        <x:v>Emanuele Ornella</x:v>
+      </x:c>
+      <x:c r="B42" s="34" t="str">
+        <x:v>emanuele ornella</x:v>
+      </x:c>
+      <x:c r="C42" s="34" t="str">
+        <x:v>2762</x:v>
+      </x:c>
+      <x:c r="D42" s="34" t="str">
+        <x:v>Emanuele Ornella</x:v>
+      </x:c>
+      <x:c r="E42" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/2762/emanuele-ornella</x:v>
+      </x:c>
+      <x:c r="F42" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/VTvlauB31O6WxXXi8Vy-uQ__previewthumb/img/Ovpz0ipB9Syn0mLlf2GbqasaSMY=/fit-in/300x320/filters:strip_icc()/pic156586.jpg</x:v>
+      </x:c>
+      <x:c r="G42" s="34" t="str">
+        <x:v>assets/designers/2762.webp</x:v>
+      </x:c>
+      <x:c r="H42" s="34" t="str">
+        <x:v>156586</x:v>
+      </x:c>
+      <x:c r="I42" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J42" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K42" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=2762&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L42" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/432067/assyria-second-edition</x:v>
+      </x:c>
+      <x:c r="M42" s="34" t="str">
+        <x:v>432067</x:v>
+      </x:c>
+      <x:c r="N42" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=432067&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O42" s="34" t="str"/>
+    </x:row>
+    <x:row r="43" ht="22" customHeight="1">
+      <x:c r="A43" s="34" t="str">
+        <x:v>Emiliano Sciarra</x:v>
+      </x:c>
+      <x:c r="B43" s="34" t="str">
+        <x:v>emiliano sciarra</x:v>
+      </x:c>
+      <x:c r="C43" s="34" t="str">
+        <x:v>1581</x:v>
+      </x:c>
+      <x:c r="D43" s="34" t="str">
+        <x:v>Emiliano Sciarra</x:v>
+      </x:c>
+      <x:c r="E43" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/1581/emiliano-sciarra</x:v>
+      </x:c>
+      <x:c r="F43" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/teMVpftfSHflUVz_6H1b4g__previewthumb/img/8NNLqdiNdSBF5Ycu-8STwR3Ub40=/fit-in/300x320/filters:strip_icc()/pic132049.jpg</x:v>
+      </x:c>
+      <x:c r="G43" s="34" t="str">
+        <x:v>assets/designers/1581.webp</x:v>
+      </x:c>
+      <x:c r="H43" s="34" t="str">
+        <x:v>132049</x:v>
+      </x:c>
+      <x:c r="I43" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J43" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K43" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=1581&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L43" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/472803/black-flag</x:v>
+      </x:c>
+      <x:c r="M43" s="34" t="str">
+        <x:v>472803</x:v>
+      </x:c>
+      <x:c r="N43" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=472803&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O43" s="34" t="str"/>
+    </x:row>
+    <x:row r="44" ht="22" customHeight="1">
+      <x:c r="A44" s="34" t="str">
+        <x:v>Fabio Lopiano</x:v>
+      </x:c>
+      <x:c r="B44" s="34" t="str">
+        <x:v>fabio lopiano</x:v>
+      </x:c>
+      <x:c r="C44" s="34" t="str">
+        <x:v>100575</x:v>
+      </x:c>
+      <x:c r="D44" s="34" t="str">
+        <x:v>Fabio Lopiano</x:v>
+      </x:c>
+      <x:c r="E44" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/100575/fabio-lopiano</x:v>
+      </x:c>
+      <x:c r="F44" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/3nu7o6xFyZRWHhfCuNo1JQ__previewthumb/img/jLfkj17Q5rGKo51TqCfYDo8Oqs8=/fit-in/300x320/filters:strip_icc()/pic8462522.jpg</x:v>
+      </x:c>
+      <x:c r="G44" s="34" t="str">
+        <x:v>assets/designers/100575.webp</x:v>
+      </x:c>
+      <x:c r="H44" s="34" t="str">
+        <x:v>8462522</x:v>
+      </x:c>
+      <x:c r="I44" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J44" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K44" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=100575&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L44" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/467253/green-city</x:v>
+      </x:c>
+      <x:c r="M44" s="34" t="str">
+        <x:v>467253</x:v>
+      </x:c>
+      <x:c r="N44" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=467253&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O44" s="34" t="str"/>
+    </x:row>
+    <x:row r="45" ht="22" customHeight="1">
+      <x:c r="A45" s="34" t="str">
+        <x:v>Frank West</x:v>
+      </x:c>
+      <x:c r="B45" s="34" t="str">
+        <x:v>frank west</x:v>
+      </x:c>
+      <x:c r="C45" s="34" t="str">
+        <x:v>94322</x:v>
+      </x:c>
+      <x:c r="D45" s="34" t="str">
+        <x:v>Frank West</x:v>
+      </x:c>
+      <x:c r="E45" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/94322/frank-west</x:v>
+      </x:c>
+      <x:c r="F45" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/OhyXKn3iwarHyBthqi2gvA__previewthumb/img/NXqf9uJ0sS8Pyf34ljEKeCRX0A4=/fit-in/300x320/filters:strip_icc()/pic3148631.jpg</x:v>
+      </x:c>
+      <x:c r="G45" s="34" t="str">
+        <x:v>assets/designers/94322.webp</x:v>
+      </x:c>
+      <x:c r="H45" s="34" t="str">
+        <x:v>3148631</x:v>
+      </x:c>
+      <x:c r="I45" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J45" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K45" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=94322&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L45" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/367375/race-to-the-raft</x:v>
+      </x:c>
+      <x:c r="M45" s="34" t="str">
+        <x:v>367375</x:v>
+      </x:c>
+      <x:c r="N45" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=367375&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O45" s="34" t="str"/>
+    </x:row>
+    <x:row r="46" ht="22" customHeight="1">
+      <x:c r="A46" s="34" t="str">
+        <x:v>Friedemann Friese</x:v>
+      </x:c>
+      <x:c r="B46" s="34" t="str">
+        <x:v>friedemann friese</x:v>
+      </x:c>
+      <x:c r="C46" s="34" t="str">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="D46" s="34" t="str">
+        <x:v>Friedemann Friese</x:v>
+      </x:c>
+      <x:c r="E46" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/141/friedemann-friese</x:v>
+      </x:c>
+      <x:c r="F46" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/7_ZFEw5Pm10fG3u6Tpiquw__previewthumb/img/C9DuoHH2Mg04bnpSL8YI9hltqMM=/fit-in/300x320/filters:strip_icc()/pic260187.jpg</x:v>
+      </x:c>
+      <x:c r="G46" s="34" t="str">
+        <x:v>assets/designers/141.webp</x:v>
+      </x:c>
+      <x:c r="H46" s="34" t="str">
+        <x:v>260187</x:v>
+      </x:c>
+      <x:c r="I46" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J46" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K46" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=141&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L46" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/7805/fearsome-floors</x:v>
+      </x:c>
+      <x:c r="M46" s="34" t="str">
+        <x:v>7805</x:v>
+      </x:c>
+      <x:c r="N46" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=7805&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O46" s="34" t="str"/>
+    </x:row>
+    <x:row r="47" ht="22" customHeight="1">
+      <x:c r="A47" s="34" t="str">
+        <x:v>Gavan Brown</x:v>
+      </x:c>
+      <x:c r="B47" s="34" t="str">
+        <x:v>gavan brown</x:v>
+      </x:c>
+      <x:c r="C47" s="34" t="str">
+        <x:v>32887</x:v>
+      </x:c>
+      <x:c r="D47" s="34" t="str">
+        <x:v>Gavan Brown</x:v>
+      </x:c>
+      <x:c r="E47" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/32887/gavan-brown</x:v>
+      </x:c>
+      <x:c r="F47" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/nd5Cn1rJOXC0PJr7TXj-SQ__previewthumb/img/UZEBPOQVJCeWU9BhSHJZXAkU6TU=/fit-in/300x320/filters:strip_icc()/pic9047853.jpg</x:v>
+      </x:c>
+      <x:c r="G47" s="34" t="str">
+        <x:v>assets/designers/32887.webp</x:v>
+      </x:c>
+      <x:c r="H47" s="34" t="str">
+        <x:v>9047853</x:v>
+      </x:c>
+      <x:c r="I47" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J47" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K47" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=32887&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L47" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/224517/brass-birmingham</x:v>
+      </x:c>
+      <x:c r="M47" s="34" t="str">
+        <x:v>224517</x:v>
+      </x:c>
+      <x:c r="N47" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=224517&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O47" s="34" t="str"/>
+    </x:row>
+    <x:row r="48" ht="22" customHeight="1">
+      <x:c r="A48" s="34" t="str">
+        <x:v>Gernot Köpke</x:v>
+      </x:c>
+      <x:c r="B48" s="34" t="str">
+        <x:v>gernot köpke</x:v>
+      </x:c>
+      <x:c r="C48" s="34" t="str">
+        <x:v>97563</x:v>
+      </x:c>
+      <x:c r="D48" s="34" t="str">
+        <x:v>Gernot Köpke</x:v>
+      </x:c>
+      <x:c r="E48" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/97563/gernot-kopke</x:v>
+      </x:c>
+      <x:c r="F48" s="34" t="str"/>
+      <x:c r="G48" s="34" t="str"/>
+      <x:c r="H48" s="34" t="str">
+        <x:v>1657690</x:v>
+      </x:c>
+      <x:c r="I48" s="34" t="str">
+        <x:v>no-image</x:v>
+      </x:c>
+      <x:c r="J48" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K48" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=97563&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L48" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/450923/the-danes</x:v>
+      </x:c>
+      <x:c r="M48" s="34" t="str">
+        <x:v>450923</x:v>
+      </x:c>
+      <x:c r="N48" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=450923&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O48" s="34" t="str">
+        <x:v>BGG 設計師個人頁使用通用缺圖圖示；BGG 個人相簿查核：圖庫未找到可確認人物照片；相簿來源：https://api.geekdo.com/api/images?ajax=1&amp;gallery=all&amp;nosession=1&amp;objectid=97563&amp;objecttype=person&amp;pageid=1&amp;showcount=10&amp;sort=hot</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="22" customHeight="1">
+      <x:c r="A49" s="34" t="str">
+        <x:v>Gordon Calleja</x:v>
+      </x:c>
+      <x:c r="B49" s="34" t="str">
+        <x:v>gordon calleja</x:v>
+      </x:c>
+      <x:c r="C49" s="34" t="str">
+        <x:v>79973</x:v>
+      </x:c>
+      <x:c r="D49" s="34" t="str">
+        <x:v>Gordon Calleja</x:v>
+      </x:c>
+      <x:c r="E49" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/79973/gordon-calleja</x:v>
+      </x:c>
+      <x:c r="F49" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/WuTDCqnwDAEgJkpiU4nHbw__previewthumb/img/kJBRtu4_MmXCQcO9YjicDq2zzXE=/fit-in/300x320/filters:strip_icc()/pic2382043.jpg</x:v>
+      </x:c>
+      <x:c r="G49" s="34" t="str">
+        <x:v>assets/designers/79973.webp</x:v>
+      </x:c>
+      <x:c r="H49" s="34" t="str">
+        <x:v>2382043</x:v>
+      </x:c>
+      <x:c r="I49" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J49" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K49" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=79973&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L49" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/292126/excavation-earth</x:v>
+      </x:c>
+      <x:c r="M49" s="34" t="str">
+        <x:v>292126</x:v>
+      </x:c>
+      <x:c r="N49" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=292126&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O49" s="34" t="str"/>
+    </x:row>
+    <x:row r="50" ht="22" customHeight="1">
+      <x:c r="A50" s="34" t="str">
+        <x:v>Guillaume Montiage</x:v>
+      </x:c>
+      <x:c r="B50" s="34" t="str">
+        <x:v>guillaume montiage</x:v>
+      </x:c>
+      <x:c r="C50" s="34" t="str">
+        <x:v>10393</x:v>
+      </x:c>
+      <x:c r="D50" s="34" t="str">
+        <x:v>Guillaume Montiage</x:v>
+      </x:c>
+      <x:c r="E50" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/10393/guillaume-montiage</x:v>
+      </x:c>
+      <x:c r="F50" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/D4_DpxkY1ZwI8eWKmua3sA__previewthumb/img/rfXphjtV76s0OnKSr7J8-iFwwU0=/fit-in/300x320/filters:strip_icc()/pic8267101.jpg</x:v>
+      </x:c>
+      <x:c r="G50" s="34" t="str">
+        <x:v>assets/designers/10393.webp</x:v>
+      </x:c>
+      <x:c r="H50" s="34" t="str">
+        <x:v>8267101</x:v>
+      </x:c>
+      <x:c r="I50" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J50" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K50" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=10393&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L50" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/466538/kemet-the-gates-of-thonis</x:v>
+      </x:c>
+      <x:c r="M50" s="34" t="str">
+        <x:v>466538</x:v>
+      </x:c>
+      <x:c r="N50" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=466538&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O50" s="34" t="str"/>
+    </x:row>
+    <x:row r="51" ht="22" customHeight="1">
+      <x:c r="A51" s="34" t="str">
+        <x:v>Hal Duncan</x:v>
+      </x:c>
+      <x:c r="B51" s="34" t="str">
+        <x:v>hal duncan</x:v>
+      </x:c>
+      <x:c r="C51" s="34" t="str">
+        <x:v>107037</x:v>
+      </x:c>
+      <x:c r="D51" s="34" t="str">
+        <x:v>Hal Duncan</x:v>
+      </x:c>
+      <x:c r="E51" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/107037/hal-duncan</x:v>
+      </x:c>
+      <x:c r="F51" s="34" t="str"/>
+      <x:c r="G51" s="34" t="str"/>
+      <x:c r="H51" s="34" t="str">
+        <x:v>1657690</x:v>
+      </x:c>
+      <x:c r="I51" s="34" t="str">
+        <x:v>no-image</x:v>
+      </x:c>
+      <x:c r="J51" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K51" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=107037&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L51" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/343274/cryptid-urban-legends</x:v>
+      </x:c>
+      <x:c r="M51" s="34" t="str">
+        <x:v>343274</x:v>
+      </x:c>
+      <x:c r="N51" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=343274&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O51" s="34" t="str">
+        <x:v>BGG 設計師個人頁使用通用缺圖圖示；BGG 個人相簿查核：圖庫無圖片；相簿來源：https://api.geekdo.com/api/images?ajax=1&amp;gallery=all&amp;nosession=1&amp;objectid=107037&amp;objecttype=person&amp;pageid=1&amp;showcount=10&amp;sort=hot</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="22" customHeight="1">
+      <x:c r="A52" s="34" t="str">
+        <x:v>Ian Hutchison</x:v>
+      </x:c>
+      <x:c r="B52" s="34" t="str">
+        <x:v>ian hutchison</x:v>
+      </x:c>
+      <x:c r="C52" s="34" t="str">
+        <x:v>173374</x:v>
+      </x:c>
+      <x:c r="D52" s="34" t="str">
+        <x:v>Ian Hutchison</x:v>
+      </x:c>
+      <x:c r="E52" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/173374/ian-hutchison</x:v>
+      </x:c>
+      <x:c r="F52" s="34" t="str"/>
+      <x:c r="G52" s="34" t="str"/>
+      <x:c r="H52" s="34" t="str">
+        <x:v>1657690</x:v>
+      </x:c>
+      <x:c r="I52" s="34" t="str">
+        <x:v>no-image</x:v>
+      </x:c>
+      <x:c r="J52" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K52" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=173374&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L52" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/462761/electrify</x:v>
+      </x:c>
+      <x:c r="M52" s="34" t="str">
+        <x:v>462761</x:v>
+      </x:c>
+      <x:c r="N52" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=462761&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O52" s="34" t="str">
+        <x:v>BGG 設計師個人頁使用通用缺圖圖示；BGG 個人相簿查核：圖庫無圖片；相簿來源：https://api.geekdo.com/api/images?ajax=1&amp;gallery=all&amp;nosession=1&amp;objectid=173374&amp;objecttype=person&amp;pageid=1&amp;showcount=10&amp;sort=hot</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="22" customHeight="1">
+      <x:c r="A53" s="34" t="str">
+        <x:v>Isaias Vallejo</x:v>
+      </x:c>
+      <x:c r="B53" s="34" t="str">
+        <x:v>isaias vallejo</x:v>
+      </x:c>
+      <x:c r="C53" s="34" t="str">
+        <x:v>48263</x:v>
+      </x:c>
+      <x:c r="D53" s="34" t="str">
+        <x:v>Isaias Vallejo</x:v>
+      </x:c>
+      <x:c r="E53" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/48263/isaias-vallejo</x:v>
+      </x:c>
+      <x:c r="F53" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/ZbEzCn5wyhEJE_y9j5FVUg__previewthumb/img/xAzU2wCEyOUZN7rcnlItCbeTPbc=/fit-in/300x320/filters:strip_icc()/pic4733826.png</x:v>
+      </x:c>
+      <x:c r="G53" s="34" t="str">
+        <x:v>assets/designers/48263.webp</x:v>
+      </x:c>
+      <x:c r="H53" s="34" t="str">
+        <x:v>4733826</x:v>
+      </x:c>
+      <x:c r="I53" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J53" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K53" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=48263&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L53" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/478370/storyfold-buried-truths</x:v>
+      </x:c>
+      <x:c r="M53" s="34" t="str">
+        <x:v>478370</x:v>
+      </x:c>
+      <x:c r="N53" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=478370&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O53" s="34" t="str"/>
+    </x:row>
+    <x:row r="54" ht="22" customHeight="1">
+      <x:c r="A54" s="34" t="str">
+        <x:v>Jacques Bariot</x:v>
+      </x:c>
+      <x:c r="B54" s="34" t="str">
+        <x:v>jacques bariot</x:v>
+      </x:c>
+      <x:c r="C54" s="34" t="str">
+        <x:v>10395</x:v>
+      </x:c>
+      <x:c r="D54" s="34" t="str">
+        <x:v>Jacques Bariot</x:v>
+      </x:c>
+      <x:c r="E54" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/10395/jacques-bariot</x:v>
+      </x:c>
+      <x:c r="F54" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/l0XLaf3dcRjFEWABe-Y8Cw__previewthumb/img/aAaq0cQP2_W2VVJO4VJMVcmd78Q=/fit-in/300x320/filters:strip_icc()/pic8267097.jpg</x:v>
+      </x:c>
+      <x:c r="G54" s="34" t="str">
+        <x:v>assets/designers/10395.webp</x:v>
+      </x:c>
+      <x:c r="H54" s="34" t="str">
+        <x:v>8267097</x:v>
+      </x:c>
+      <x:c r="I54" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J54" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K54" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=10395&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L54" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/466538/kemet-the-gates-of-thonis</x:v>
+      </x:c>
+      <x:c r="M54" s="34" t="str">
+        <x:v>466538</x:v>
+      </x:c>
+      <x:c r="N54" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=466538&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O54" s="34" t="str"/>
+    </x:row>
+    <x:row r="55" ht="22" customHeight="1">
+      <x:c r="A55" s="34" t="str">
+        <x:v>James Kniffen</x:v>
+      </x:c>
+      <x:c r="B55" s="34" t="str">
+        <x:v>james kniffen</x:v>
+      </x:c>
+      <x:c r="C55" s="34" t="str">
+        <x:v>64445</x:v>
+      </x:c>
+      <x:c r="D55" s="34" t="str">
+        <x:v>James Kniffen</x:v>
+      </x:c>
+      <x:c r="E55" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/64445/james-kniffen</x:v>
+      </x:c>
+      <x:c r="F55" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/OinVHHukUZu3uPNop9j_8g__previewthumb/img/RX1_24MpFq3EwYbaJljPK3qWo3I=/fit-in/300x320/filters:strip_icc()/pic2450024.jpg</x:v>
+      </x:c>
+      <x:c r="G55" s="34" t="str">
+        <x:v>assets/designers/64445.webp</x:v>
+      </x:c>
+      <x:c r="H55" s="34" t="str">
+        <x:v>2450024</x:v>
+      </x:c>
+      <x:c r="I55" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J55" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K55" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=64445&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L55" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/175155/forbidden-stars</x:v>
+      </x:c>
+      <x:c r="M55" s="34" t="str">
+        <x:v>175155</x:v>
+      </x:c>
+      <x:c r="N55" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=175155&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O55" s="34" t="str"/>
+    </x:row>
+    <x:row r="56" ht="22" customHeight="1">
+      <x:c r="A56" s="34" t="str">
+        <x:v>James Van Niekerk</x:v>
+      </x:c>
+      <x:c r="B56" s="34" t="str">
+        <x:v>james van niekerk</x:v>
+      </x:c>
+      <x:c r="C56" s="34" t="str">
+        <x:v>75188</x:v>
+      </x:c>
+      <x:c r="D56" s="34" t="str">
+        <x:v>James Van Niekerk</x:v>
+      </x:c>
+      <x:c r="E56" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/75188/james-van-niekerk</x:v>
+      </x:c>
+      <x:c r="F56" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/RscBEmrA_aElx9WAzfYcrg__previewthumb/img/bOosDexgMS2UTV7VNfqUo-ImpsI=/fit-in/300x320/filters:strip_icc()/pic6157006.jpg</x:v>
+      </x:c>
+      <x:c r="G56" s="34" t="str">
+        <x:v>assets/designers/75188.webp</x:v>
+      </x:c>
+      <x:c r="H56" s="34" t="str">
+        <x:v>6157006</x:v>
+      </x:c>
+      <x:c r="I56" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J56" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K56" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=75188&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L56" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/325889/valor-and-villainy-lludwiks-labyrinth</x:v>
+      </x:c>
+      <x:c r="M56" s="34" t="str">
+        <x:v>325889</x:v>
+      </x:c>
+      <x:c r="N56" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=325889&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O56" s="34" t="str"/>
+    </x:row>
+    <x:row r="57" ht="22" customHeight="1">
+      <x:c r="A57" s="34" t="str">
+        <x:v>Jamey Stegmaier</x:v>
+      </x:c>
+      <x:c r="B57" s="34" t="str">
+        <x:v>jamey stegmaier</x:v>
+      </x:c>
+      <x:c r="C57" s="34" t="str">
+        <x:v>62640</x:v>
+      </x:c>
+      <x:c r="D57" s="34" t="str">
+        <x:v>Jamey Stegmaier</x:v>
+      </x:c>
+      <x:c r="E57" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/62640/jamey-stegmaier</x:v>
+      </x:c>
+      <x:c r="F57" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/9eWZUGINva8Kha_J0qDg4Q__previewthumb/img/ZVc6OytMbmp96mznOJ_ZpKdppkc=/fit-in/300x320/filters:strip_icc()/pic1403066.jpg</x:v>
+      </x:c>
+      <x:c r="G57" s="34" t="str">
+        <x:v>assets/designers/62640.webp</x:v>
+      </x:c>
+      <x:c r="H57" s="34" t="str">
+        <x:v>1403066</x:v>
+      </x:c>
+      <x:c r="I57" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J57" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K57" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=62640&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L57" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/356035/terra-mystica-fan-factions</x:v>
+      </x:c>
+      <x:c r="M57" s="34" t="str">
+        <x:v>356035</x:v>
+      </x:c>
+      <x:c r="N57" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=356035&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O57" s="34" t="str"/>
+    </x:row>
+    <x:row r="58" ht="22" customHeight="1">
+      <x:c r="A58" s="34" t="str">
+        <x:v>Jamie Jolly</x:v>
+      </x:c>
+      <x:c r="B58" s="34" t="str">
+        <x:v>jamie jolly</x:v>
+      </x:c>
+      <x:c r="C58" s="34" t="str">
+        <x:v>99777</x:v>
+      </x:c>
+      <x:c r="D58" s="34" t="str">
+        <x:v>Jamie Jolly</x:v>
+      </x:c>
+      <x:c r="E58" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/99777/jamie-jolly</x:v>
+      </x:c>
+      <x:c r="F58" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/q4Vu1jsJ9XuEcjs_0pfyFw__previewthumb/img/aO3UfqY5AKqPqAhDY-9tdFEpuGg=/fit-in/300x320/filters:strip_icc()/pic5289846.jpg</x:v>
+      </x:c>
+      <x:c r="G58" s="34" t="str">
+        <x:v>assets/designers/99777.webp</x:v>
+      </x:c>
+      <x:c r="H58" s="34" t="str">
+        <x:v>5289846</x:v>
+      </x:c>
+      <x:c r="I58" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J58" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K58" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=99777&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L58" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/476866/avalon-the-riven-veil-mistwalkers-expansion</x:v>
+      </x:c>
+      <x:c r="M58" s="34" t="str">
+        <x:v>476866</x:v>
+      </x:c>
+      <x:c r="N58" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=476866&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O58" s="34" t="str"/>
+    </x:row>
+    <x:row r="59" ht="22" customHeight="1">
+      <x:c r="A59" s="34" t="str">
+        <x:v>Jan M. Gonzalez</x:v>
+      </x:c>
+      <x:c r="B59" s="34" t="str">
+        <x:v>jan m. gonzalez</x:v>
+      </x:c>
+      <x:c r="C59" s="34" t="str">
+        <x:v>102517</x:v>
+      </x:c>
+      <x:c r="D59" s="34" t="str">
+        <x:v>Jan M. Gonzalez</x:v>
+      </x:c>
+      <x:c r="E59" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/102517/jan-m-gonzalez</x:v>
+      </x:c>
+      <x:c r="F59" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/eosSskusBtBS0fKjPBq1bw__previewthumb/img/B8voxB01vF26yu04P58Cso7XKds=/fit-in/300x320/filters:strip_icc()/pic5443677.jpg</x:v>
+      </x:c>
+      <x:c r="G59" s="34" t="str">
+        <x:v>assets/designers/102517.webp</x:v>
+      </x:c>
+      <x:c r="H59" s="34" t="str">
+        <x:v>5443677</x:v>
+      </x:c>
+      <x:c r="I59" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J59" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K59" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=102517&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L59" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/375573/manhattan-project-war-machine</x:v>
+      </x:c>
+      <x:c r="M59" s="34" t="str">
+        <x:v>375573</x:v>
+      </x:c>
+      <x:c r="N59" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=375573&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O59" s="34" t="str"/>
+    </x:row>
+    <x:row r="60" ht="22" customHeight="1">
+      <x:c r="A60" s="34" t="str">
+        <x:v>Javier Martínez Gómez</x:v>
+      </x:c>
+      <x:c r="B60" s="34" t="str">
+        <x:v>javier martínez gómez</x:v>
+      </x:c>
+      <x:c r="C60" s="34" t="str">
+        <x:v>120179</x:v>
+      </x:c>
+      <x:c r="D60" s="34" t="str">
+        <x:v>Javier Martínez Gómez</x:v>
+      </x:c>
+      <x:c r="E60" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/120179/javier-martinez-gomez</x:v>
+      </x:c>
+      <x:c r="F60" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/Xtj-VBJEWS5eSM5emZjW4g__previewthumb/img/Z-a7VdnCknUlixJVEo9Ri7t38z0=/fit-in/300x320/filters:strip_icc()/pic5471442.jpg</x:v>
+      </x:c>
+      <x:c r="G60" s="34" t="str">
+        <x:v>assets/designers/120179.webp</x:v>
+      </x:c>
+      <x:c r="H60" s="34" t="str">
+        <x:v>5471442</x:v>
+      </x:c>
+      <x:c r="I60" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J60" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K60" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=120179&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L60" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/469223/axia-slayer-combo</x:v>
+      </x:c>
+      <x:c r="M60" s="34" t="str">
+        <x:v>469223</x:v>
+      </x:c>
+      <x:c r="N60" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=469223&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O60" s="34" t="str"/>
+    </x:row>
+    <x:row r="61" ht="22" customHeight="1">
+      <x:c r="A61" s="34" t="str">
+        <x:v>John D. Clair</x:v>
+      </x:c>
+      <x:c r="B61" s="34" t="str">
+        <x:v>john d. clair</x:v>
+      </x:c>
+      <x:c r="C61" s="34" t="str">
+        <x:v>57723</x:v>
+      </x:c>
+      <x:c r="D61" s="34" t="str">
+        <x:v>John D. Clair</x:v>
+      </x:c>
+      <x:c r="E61" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/57723/john-d-clair</x:v>
+      </x:c>
+      <x:c r="F61" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/OXR8slvI6_QKxitspZpeQA__previewthumb/img/lSgAUG6ABd8NNeF1R0CDiYvKQg8=/fit-in/300x320/filters:strip_icc()/pic9687142.jpg</x:v>
+      </x:c>
+      <x:c r="G61" s="34" t="str">
+        <x:v>assets/designers/57723.webp</x:v>
+      </x:c>
+      <x:c r="H61" s="34" t="str">
+        <x:v>9687142</x:v>
+      </x:c>
+      <x:c r="I61" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J61" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K61" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=57723&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L61" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/462761/electrify</x:v>
+      </x:c>
+      <x:c r="M61" s="34" t="str">
+        <x:v>462761</x:v>
+      </x:c>
+      <x:c r="N61" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=462761&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O61" s="34" t="str"/>
+    </x:row>
+    <x:row r="62" ht="22" customHeight="1">
+      <x:c r="A62" s="34" t="str">
+        <x:v>Jonny Pac</x:v>
+      </x:c>
+      <x:c r="B62" s="34" t="str">
+        <x:v>jonny pac</x:v>
+      </x:c>
+      <x:c r="C62" s="34" t="str">
+        <x:v>69851</x:v>
+      </x:c>
+      <x:c r="D62" s="34" t="str">
+        <x:v>Jonny Pac</x:v>
+      </x:c>
+      <x:c r="E62" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/69851/jonny-pac</x:v>
+      </x:c>
+      <x:c r="F62" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/LZWFHlGLoM3dhgzVFTN5uQ__previewthumb/img/wFrc-0zzxeNk7fUPL-qeAsA2N30=/fit-in/300x320/filters:strip_icc()/pic7155418.jpg</x:v>
+      </x:c>
+      <x:c r="G62" s="34" t="str">
+        <x:v>assets/designers/69851.webp</x:v>
+      </x:c>
+      <x:c r="H62" s="34" t="str">
+        <x:v>7155418</x:v>
+      </x:c>
+      <x:c r="I62" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J62" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K62" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=69851&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L62" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/467500/life-along-floe</x:v>
+      </x:c>
+      <x:c r="M62" s="34" t="str">
+        <x:v>467500</x:v>
+      </x:c>
+      <x:c r="N62" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=467500&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O62" s="34" t="str"/>
+    </x:row>
+    <x:row r="63" ht="22" customHeight="1">
+      <x:c r="A63" s="34" t="str">
+        <x:v>Joseph Summa</x:v>
+      </x:c>
+      <x:c r="B63" s="34" t="str">
+        <x:v>joseph summa</x:v>
+      </x:c>
+      <x:c r="C63" s="34" t="str">
+        <x:v>150628</x:v>
+      </x:c>
+      <x:c r="D63" s="34" t="str">
+        <x:v>Joseph Summa</x:v>
+      </x:c>
+      <x:c r="E63" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/150628/joseph-summa</x:v>
+      </x:c>
+      <x:c r="F63" s="34" t="str"/>
+      <x:c r="G63" s="34" t="str"/>
+      <x:c r="H63" s="34" t="str">
+        <x:v>1657690</x:v>
+      </x:c>
+      <x:c r="I63" s="34" t="str">
+        <x:v>no-image</x:v>
+      </x:c>
+      <x:c r="J63" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K63" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=150628&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L63" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/378291/beyond-the-sun-leaders-of-the-new-dawn</x:v>
+      </x:c>
+      <x:c r="M63" s="34" t="str">
+        <x:v>378291</x:v>
+      </x:c>
+      <x:c r="N63" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=378291&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O63" s="34" t="str">
+        <x:v>BGG 設計師個人頁使用通用缺圖圖示；BGG 個人相簿查核：圖庫無圖片；相簿來源：https://api.geekdo.com/api/images?ajax=1&amp;gallery=all&amp;nosession=1&amp;objectid=150628&amp;objecttype=person&amp;pageid=1&amp;showcount=10&amp;sort=hot</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" ht="22" customHeight="1">
+      <x:c r="A64" s="34" t="str">
+        <x:v>Josh Wood</x:v>
+      </x:c>
+      <x:c r="B64" s="34" t="str">
+        <x:v>josh wood</x:v>
+      </x:c>
+      <x:c r="C64" s="34" t="str">
+        <x:v>101567</x:v>
+      </x:c>
+      <x:c r="D64" s="34" t="str">
+        <x:v>Josh Wood</x:v>
+      </x:c>
+      <x:c r="E64" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/101567/josh-wood</x:v>
+      </x:c>
+      <x:c r="F64" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/l6jsjbLrPsKxohQqCQqR5g__previewthumb/img/pj2GvhyC_W13bmVKVbe69DyYxlY=/fit-in/300x320/filters:strip_icc()/pic8364250.jpg</x:v>
+      </x:c>
+      <x:c r="G64" s="34" t="str">
+        <x:v>assets/designers/101567.webp</x:v>
+      </x:c>
+      <x:c r="H64" s="34" t="str">
+        <x:v>8364250</x:v>
+      </x:c>
+      <x:c r="I64" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J64" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K64" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=101567&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L64" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/228504/cat-lady</x:v>
+      </x:c>
+      <x:c r="M64" s="34" t="str">
+        <x:v>228504</x:v>
+      </x:c>
+      <x:c r="N64" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=228504&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O64" s="34" t="str"/>
+    </x:row>
+    <x:row r="65" ht="22" customHeight="1">
+      <x:c r="A65" s="34" t="str">
+        <x:v>Julian Birke</x:v>
+      </x:c>
+      <x:c r="B65" s="34" t="str">
+        <x:v>julian birke</x:v>
+      </x:c>
+      <x:c r="C65" s="34" t="str">
+        <x:v>177350</x:v>
+      </x:c>
+      <x:c r="D65" s="34" t="str">
+        <x:v>Julian Birke</x:v>
+      </x:c>
+      <x:c r="E65" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/177350/julian-birke</x:v>
+      </x:c>
+      <x:c r="F65" s="34" t="str"/>
+      <x:c r="G65" s="34" t="str"/>
+      <x:c r="H65" s="34" t="str">
+        <x:v>1657690</x:v>
+      </x:c>
+      <x:c r="I65" s="34" t="str">
+        <x:v>no-image</x:v>
+      </x:c>
+      <x:c r="J65" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K65" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=177350&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L65" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/478504/pincer-a-gentlemans-war</x:v>
+      </x:c>
+      <x:c r="M65" s="34" t="str">
+        <x:v>478504</x:v>
+      </x:c>
+      <x:c r="N65" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=478504&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O65" s="34" t="str">
+        <x:v>BGG 設計師個人頁使用通用缺圖圖示；BGG 個人相簿查核：圖庫無圖片；相簿來源：https://api.geekdo.com/api/images?ajax=1&amp;gallery=all&amp;nosession=1&amp;objectid=177350&amp;objecttype=person&amp;pageid=1&amp;showcount=10&amp;sort=hot</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" ht="22" customHeight="1">
+      <x:c r="A66" s="34" t="str">
+        <x:v>Juno Schaaffhausen Te'o</x:v>
+      </x:c>
+      <x:c r="B66" s="34" t="str">
+        <x:v>juno schaaffhausen te'o</x:v>
+      </x:c>
+      <x:c r="C66" s="34" t="str">
+        <x:v>171225</x:v>
+      </x:c>
+      <x:c r="D66" s="34" t="str">
+        <x:v>Juno Schaaffhausen Te'o</x:v>
+      </x:c>
+      <x:c r="E66" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/171225/juno-schaaffhausen-teo</x:v>
+      </x:c>
+      <x:c r="F66" s="34" t="str"/>
+      <x:c r="G66" s="34" t="str"/>
+      <x:c r="H66" s="34" t="str">
+        <x:v>1657690</x:v>
+      </x:c>
+      <x:c r="I66" s="34" t="str">
+        <x:v>no-image</x:v>
+      </x:c>
+      <x:c r="J66" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K66" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=171225&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L66" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/455519/isle-of-feathers</x:v>
+      </x:c>
+      <x:c r="M66" s="34" t="str">
+        <x:v>455519</x:v>
+      </x:c>
+      <x:c r="N66" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=455519&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O66" s="34" t="str">
+        <x:v>BGG 設計師個人頁使用通用缺圖圖示；BGG 個人相簿查核：圖庫無圖片；相簿來源：https://api.geekdo.com/api/images?ajax=1&amp;gallery=all&amp;nosession=1&amp;objectid=171225&amp;objecttype=person&amp;pageid=1&amp;showcount=10&amp;sort=hot</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="22" customHeight="1">
+      <x:c r="A67" s="34" t="str">
+        <x:v>Kedric Winks</x:v>
+      </x:c>
+      <x:c r="B67" s="34" t="str">
+        <x:v>kedric winks</x:v>
+      </x:c>
+      <x:c r="C67" s="34" t="str">
+        <x:v>74267</x:v>
+      </x:c>
+      <x:c r="D67" s="34" t="str">
+        <x:v>Kedric Winks</x:v>
+      </x:c>
+      <x:c r="E67" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/74267/kedric-winks</x:v>
+      </x:c>
+      <x:c r="F67" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/xp2-bNU5X9J30yByzdtmfg__previewthumb/img/MC9cQgXd7HD2de--Vw5Moe0NWCw=/fit-in/300x320/filters:strip_icc()/pic8951037.jpg</x:v>
+      </x:c>
+      <x:c r="G67" s="34" t="str">
+        <x:v>assets/designers/74267.webp</x:v>
+      </x:c>
+      <x:c r="H67" s="34" t="str">
+        <x:v>8951037</x:v>
+      </x:c>
+      <x:c r="I67" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J67" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K67" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=74267&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L67" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/466548/flora-funga</x:v>
+      </x:c>
+      <x:c r="M67" s="34" t="str">
+        <x:v>466548</x:v>
+      </x:c>
+      <x:c r="N67" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=466548&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O67" s="34" t="str"/>
+    </x:row>
+    <x:row r="68" ht="22" customHeight="1">
+      <x:c r="A68" s="34" t="str">
+        <x:v>Kenneth Minde</x:v>
+      </x:c>
+      <x:c r="B68" s="34" t="str">
+        <x:v>kenneth minde</x:v>
+      </x:c>
+      <x:c r="C68" s="34" t="str">
+        <x:v>81911</x:v>
+      </x:c>
+      <x:c r="D68" s="34" t="str">
+        <x:v>Kenneth Minde</x:v>
+      </x:c>
+      <x:c r="E68" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/81911/kenneth-minde</x:v>
+      </x:c>
+      <x:c r="F68" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/pIM_GgyaPHavj9knrsVDKw__previewthumb/img/F7EkzfDvpgBls7V4-qjLx62_r-o=/fit-in/300x320/filters:strip_icc()/pic2506640.png</x:v>
+      </x:c>
+      <x:c r="G68" s="34" t="str">
+        <x:v>assets/designers/81911.webp</x:v>
+      </x:c>
+      <x:c r="H68" s="34" t="str">
+        <x:v>2506640</x:v>
+      </x:c>
+      <x:c r="I68" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J68" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K68" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=81911&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L68" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/462479/timespan</x:v>
+      </x:c>
+      <x:c r="M68" s="34" t="str">
+        <x:v>462479</x:v>
+      </x:c>
+      <x:c r="N68" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=462479&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O68" s="34" t="str"/>
+    </x:row>
+    <x:row r="69" ht="22" customHeight="1">
+      <x:c r="A69" s="34" t="str">
+        <x:v>Koltin Thompson</x:v>
+      </x:c>
+      <x:c r="B69" s="34" t="str">
+        <x:v>koltin thompson</x:v>
+      </x:c>
+      <x:c r="C69" s="34" t="str">
+        <x:v>128912</x:v>
+      </x:c>
+      <x:c r="D69" s="34" t="str">
+        <x:v>Koltin Thompson</x:v>
+      </x:c>
+      <x:c r="E69" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/128912/koltin-thompson</x:v>
+      </x:c>
+      <x:c r="F69" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/srWI6bcRh4F9aSURXGd3zg__previewthumb/img/R1_JImbl7yaPjieWk6qEAoQft6Y=/fit-in/300x320/filters:strip_icc()/pic9836894.jpg</x:v>
+      </x:c>
+      <x:c r="G69" s="34" t="str">
+        <x:v>assets/designers/128912.webp</x:v>
+      </x:c>
+      <x:c r="H69" s="34" t="str">
+        <x:v>9836894</x:v>
+      </x:c>
+      <x:c r="I69" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J69" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K69" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=128912&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L69" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/470410/galactic-cruise-perfect-planning-promo-card</x:v>
+      </x:c>
+      <x:c r="M69" s="34" t="str">
+        <x:v>470410</x:v>
+      </x:c>
+      <x:c r="N69" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=470410&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O69" s="34" t="str"/>
+    </x:row>
+    <x:row r="70" ht="22" customHeight="1">
+      <x:c r="A70" s="34" t="str">
+        <x:v>Kory Jordan</x:v>
+      </x:c>
+      <x:c r="B70" s="34" t="str">
+        <x:v>kory jordan</x:v>
+      </x:c>
+      <x:c r="C70" s="34" t="str">
+        <x:v>159494</x:v>
+      </x:c>
+      <x:c r="D70" s="34" t="str">
+        <x:v>Kory Jordan</x:v>
+      </x:c>
+      <x:c r="E70" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/159494/kory-jordan</x:v>
+      </x:c>
+      <x:c r="F70" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/ODFt3Tf7kdv1ujPajCtpMw__previewthumb/img/eqk1gXRVYCAZ7MTJZSHv04ijwIM=/fit-in/300x320/filters:strip_icc()/pic8013354.jpg</x:v>
+      </x:c>
+      <x:c r="G70" s="34" t="str">
+        <x:v>assets/designers/159494.webp</x:v>
+      </x:c>
+      <x:c r="H70" s="34" t="str">
+        <x:v>8013354</x:v>
+      </x:c>
+      <x:c r="I70" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J70" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K70" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=159494&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L70" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/442093/class-of-89</x:v>
+      </x:c>
+      <x:c r="M70" s="34" t="str">
+        <x:v>442093</x:v>
+      </x:c>
+      <x:c r="N70" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=442093&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O70" s="34" t="str"/>
+    </x:row>
+    <x:row r="71" ht="22" customHeight="1">
+      <x:c r="A71" s="34" t="str">
+        <x:v>Kristian Amundsen Østby</x:v>
+      </x:c>
+      <x:c r="B71" s="34" t="str">
+        <x:v>kristian amundsen østby</x:v>
+      </x:c>
+      <x:c r="C71" s="34" t="str">
+        <x:v>4063</x:v>
+      </x:c>
+      <x:c r="D71" s="34" t="str">
+        <x:v>Kristian Amundsen Østby</x:v>
+      </x:c>
+      <x:c r="E71" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/4063/kristian-amundsen-ostby</x:v>
+      </x:c>
+      <x:c r="F71" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/BxgG3pT_pNE0SML0_dyHOw__previewthumb/img/Q0rtQ1G7316hvY5_OpXwe1H1ImY=/fit-in/300x320/filters:strip_icc()/pic7549191.jpg</x:v>
+      </x:c>
+      <x:c r="G71" s="34" t="str">
+        <x:v>assets/designers/4063.webp</x:v>
+      </x:c>
+      <x:c r="H71" s="34" t="str">
+        <x:v>7549191</x:v>
+      </x:c>
+      <x:c r="I71" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J71" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K71" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=4063&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L71" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/462479/timespan</x:v>
+      </x:c>
+      <x:c r="M71" s="34" t="str">
+        <x:v>462479</x:v>
+      </x:c>
+      <x:c r="N71" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=462479&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O71" s="34" t="str"/>
+    </x:row>
+    <x:row r="72" ht="22" customHeight="1">
+      <x:c r="A72" s="34" t="str">
+        <x:v>Luke Laurie</x:v>
+      </x:c>
+      <x:c r="B72" s="34" t="str">
+        <x:v>luke laurie</x:v>
+      </x:c>
+      <x:c r="C72" s="34" t="str">
+        <x:v>63686</x:v>
+      </x:c>
+      <x:c r="D72" s="34" t="str">
+        <x:v>Luke Laurie</x:v>
+      </x:c>
+      <x:c r="E72" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/63686/luke-laurie</x:v>
+      </x:c>
+      <x:c r="F72" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/0jHIIc9_Dpni5KvXFJxRUA__previewthumb/img/DVUK7kxGKBT4KIqiqCu_Auxc1LM=/fit-in/300x320/filters:strip_icc()/pic1732536.jpg</x:v>
+      </x:c>
+      <x:c r="G72" s="34" t="str">
+        <x:v>assets/designers/63686.webp</x:v>
+      </x:c>
+      <x:c r="H72" s="34" t="str">
+        <x:v>1732536</x:v>
+      </x:c>
+      <x:c r="I72" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J72" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K72" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=63686&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L72" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/452835/andromedas-edge-genesis</x:v>
+      </x:c>
+      <x:c r="M72" s="34" t="str">
+        <x:v>452835</x:v>
+      </x:c>
+      <x:c r="N72" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=452835&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O72" s="34" t="str"/>
+    </x:row>
+    <x:row r="73" ht="22" customHeight="1">
+      <x:c r="A73" s="34" t="str">
+        <x:v>Madison O'Neil</x:v>
+      </x:c>
+      <x:c r="B73" s="34" t="str">
+        <x:v>madison o'neil</x:v>
+      </x:c>
+      <x:c r="C73" s="34" t="str">
+        <x:v>147589</x:v>
+      </x:c>
+      <x:c r="D73" s="34" t="str">
+        <x:v>Madison O'Neil</x:v>
+      </x:c>
+      <x:c r="E73" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/147589/madison-oneil</x:v>
+      </x:c>
+      <x:c r="F73" s="34" t="str"/>
+      <x:c r="G73" s="34" t="str"/>
+      <x:c r="H73" s="34" t="str">
+        <x:v>1657690</x:v>
+      </x:c>
+      <x:c r="I73" s="34" t="str">
+        <x:v>no-image</x:v>
+      </x:c>
+      <x:c r="J73" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K73" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=147589&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L73" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/341027/heroes-of-barcadia</x:v>
+      </x:c>
+      <x:c r="M73" s="34" t="str">
+        <x:v>341027</x:v>
+      </x:c>
+      <x:c r="N73" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=341027&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O73" s="34" t="str">
+        <x:v>BGG 設計師個人頁使用通用缺圖圖示；BGG 個人相簿查核：圖庫無圖片；相簿來源：https://api.geekdo.com/api/images?ajax=1&amp;gallery=all&amp;nosession=1&amp;objectid=147589&amp;objecttype=person&amp;pageid=1&amp;showcount=10&amp;sort=hot</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" ht="22" customHeight="1">
+      <x:c r="A74" s="34" t="str">
+        <x:v>Marissa Misura</x:v>
+      </x:c>
+      <x:c r="B74" s="34" t="str">
+        <x:v>marissa misura</x:v>
+      </x:c>
+      <x:c r="C74" s="34" t="str">
+        <x:v>105447</x:v>
+      </x:c>
+      <x:c r="D74" s="34" t="str">
+        <x:v>Marissa Misura</x:v>
+      </x:c>
+      <x:c r="E74" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/105447/marissa-misura</x:v>
+      </x:c>
+      <x:c r="F74" s="34" t="str"/>
+      <x:c r="G74" s="34" t="str"/>
+      <x:c r="H74" s="34" t="str">
+        <x:v>1657690</x:v>
+      </x:c>
+      <x:c r="I74" s="34" t="str">
+        <x:v>no-image</x:v>
+      </x:c>
+      <x:c r="J74" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K74" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=105447&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L74" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/318009/dinosaur-island-rawr-n-write</x:v>
+      </x:c>
+      <x:c r="M74" s="34" t="str">
+        <x:v>318009</x:v>
+      </x:c>
+      <x:c r="N74" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=318009&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O74" s="34" t="str">
+        <x:v>BGG 設計師個人頁使用通用缺圖圖示；BGG 個人相簿查核：圖庫無圖片；相簿來源：https://api.geekdo.com/api/images?ajax=1&amp;gallery=all&amp;nosession=1&amp;objectid=105447&amp;objecttype=person&amp;pageid=1&amp;showcount=10&amp;sort=hot</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" ht="22" customHeight="1">
+      <x:c r="A75" s="34" t="str">
+        <x:v>Mark K. Swanson</x:v>
+      </x:c>
+      <x:c r="B75" s="34" t="str">
+        <x:v>mark k. swanson</x:v>
+      </x:c>
+      <x:c r="C75" s="34" t="str">
+        <x:v>77297</x:v>
+      </x:c>
+      <x:c r="D75" s="34" t="str">
+        <x:v>Mark K. Swanson</x:v>
+      </x:c>
+      <x:c r="E75" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/77297/mark-k-swanson</x:v>
+      </x:c>
+      <x:c r="F75" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/9ekhhiJeklwchm-ACosxJg__previewthumb/img/OvlZHQj51jKptsMonuGHLqwkWUw=/fit-in/300x320/filters:strip_icc()/pic3173441.jpg</x:v>
+      </x:c>
+      <x:c r="G75" s="34" t="str">
+        <x:v>assets/designers/77297.webp</x:v>
+      </x:c>
+      <x:c r="H75" s="34" t="str">
+        <x:v>3173441</x:v>
+      </x:c>
+      <x:c r="I75" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J75" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K75" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=77297&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L75" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/446669/flockers</x:v>
+      </x:c>
+      <x:c r="M75" s="34" t="str">
+        <x:v>446669</x:v>
+      </x:c>
+      <x:c r="N75" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=446669&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O75" s="34" t="str"/>
+    </x:row>
+    <x:row r="76" ht="22" customHeight="1">
+      <x:c r="A76" s="34" t="str">
+        <x:v>Martin Wallace</x:v>
+      </x:c>
+      <x:c r="B76" s="34" t="str">
+        <x:v>martin wallace</x:v>
+      </x:c>
+      <x:c r="C76" s="34" t="str">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D76" s="34" t="str">
+        <x:v>Martin Wallace</x:v>
+      </x:c>
+      <x:c r="E76" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/6/martin-wallace</x:v>
+      </x:c>
+      <x:c r="F76" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/jHCDksTsNt5Z1Nj8BvPFdw__previewthumb/img/bUPkIvlUEQJ6l_SP8_EaKFl-CgU=/fit-in/300x320/filters:strip_icc()/pic5016940.jpg</x:v>
+      </x:c>
+      <x:c r="G76" s="34" t="str">
+        <x:v>assets/designers/6.webp</x:v>
+      </x:c>
+      <x:c r="H76" s="34" t="str">
+        <x:v>5016940</x:v>
+      </x:c>
+      <x:c r="I76" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J76" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K76" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=6&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L76" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/224517/brass-birmingham</x:v>
+      </x:c>
+      <x:c r="M76" s="34" t="str">
+        <x:v>224517</x:v>
+      </x:c>
+      <x:c r="N76" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=224517&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O76" s="34" t="str"/>
+    </x:row>
+    <x:row r="77" ht="22" customHeight="1">
+      <x:c r="A77" s="34" t="str">
+        <x:v>Matt Gilbert</x:v>
+      </x:c>
+      <x:c r="B77" s="34" t="str">
+        <x:v>matt gilbert</x:v>
+      </x:c>
+      <x:c r="C77" s="34" t="str">
+        <x:v>106328</x:v>
+      </x:c>
+      <x:c r="D77" s="34" t="str">
+        <x:v>Matt Gilbert</x:v>
+      </x:c>
+      <x:c r="E77" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/106328/matt-gilbert</x:v>
+      </x:c>
+      <x:c r="F77" s="34" t="str"/>
+      <x:c r="G77" s="34" t="str"/>
+      <x:c r="H77" s="34" t="str">
+        <x:v>1657690</x:v>
+      </x:c>
+      <x:c r="I77" s="34" t="str">
+        <x:v>no-image</x:v>
+      </x:c>
+      <x:c r="J77" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K77" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=106328&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L77" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/397788</x:v>
+      </x:c>
+      <x:c r="M77" s="34" t="str">
+        <x:v>397788</x:v>
+      </x:c>
+      <x:c r="N77" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=397788&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O77" s="34" t="str">
+        <x:v>原始遊戲 ID 324590 已依 README 已核對更正為 397788，以正確遊戲署名確認設計師身分；BGG 設計師個人頁尚未提供主要照片；BGG 個人相簿查核：圖庫無圖片；相簿來源：https://api.geekdo.com/api/images?ajax=1&amp;gallery=all&amp;nosession=1&amp;objectid=106328&amp;objecttype=person&amp;pageid=1&amp;showcount=10&amp;sort=hot</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" ht="22" customHeight="1">
+      <x:c r="A78" s="34" t="str">
+        <x:v>Matt Tolman</x:v>
+      </x:c>
+      <x:c r="B78" s="34" t="str">
+        <x:v>matt tolman</x:v>
+      </x:c>
+      <x:c r="C78" s="34" t="str">
+        <x:v>32943</x:v>
+      </x:c>
+      <x:c r="D78" s="34" t="str">
+        <x:v>Matt Tolman</x:v>
+      </x:c>
+      <x:c r="E78" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/32943/matt-tolman</x:v>
+      </x:c>
+      <x:c r="F78" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/QMQSCThGe1HZZJH8spfdnw__previewthumb/img/a-uxHQKQYpd1YJ52UobGkw0dgoc=/fit-in/300x320/filters:strip_icc()/pic618337.jpg</x:v>
+      </x:c>
+      <x:c r="G78" s="34" t="str">
+        <x:v>assets/designers/32943.webp</x:v>
+      </x:c>
+      <x:c r="H78" s="34" t="str">
+        <x:v>618337</x:v>
+      </x:c>
+      <x:c r="I78" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J78" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K78" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=32943&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L78" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/224517/brass-birmingham</x:v>
+      </x:c>
+      <x:c r="M78" s="34" t="str">
+        <x:v>224517</x:v>
+      </x:c>
+      <x:c r="N78" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=224517&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O78" s="34" t="str"/>
+    </x:row>
+    <x:row r="79" ht="22" customHeight="1">
+      <x:c r="A79" s="34" t="str">
+        <x:v>Max Anderson</x:v>
+      </x:c>
+      <x:c r="B79" s="34" t="str">
+        <x:v>max anderson</x:v>
+      </x:c>
+      <x:c r="C79" s="34" t="str">
+        <x:v>114961</x:v>
+      </x:c>
+      <x:c r="D79" s="34" t="str">
+        <x:v>Max Anderson</x:v>
+      </x:c>
+      <x:c r="E79" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/114961/max-anderson</x:v>
+      </x:c>
+      <x:c r="F79" s="34" t="str"/>
+      <x:c r="G79" s="34" t="str"/>
+      <x:c r="H79" s="34" t="str">
+        <x:v>1657690</x:v>
+      </x:c>
+      <x:c r="I79" s="34" t="str">
+        <x:v>no-image</x:v>
+      </x:c>
+      <x:c r="J79" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K79" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=114961&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L79" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/270239/moonrakers</x:v>
+      </x:c>
+      <x:c r="M79" s="34" t="str">
+        <x:v>270239</x:v>
+      </x:c>
+      <x:c r="N79" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=270239&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O79" s="34" t="str">
+        <x:v>BGG 設計師個人頁使用通用缺圖圖示；BGG 個人相簿查核：圖庫無圖片；相簿來源：https://api.geekdo.com/api/images?ajax=1&amp;gallery=all&amp;nosession=1&amp;objectid=114961&amp;objecttype=person&amp;pageid=1&amp;showcount=10&amp;sort=hot</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" ht="22" customHeight="1">
+      <x:c r="A80" s="34" t="str">
+        <x:v>Maxime Rambourg</x:v>
+      </x:c>
+      <x:c r="B80" s="34" t="str">
+        <x:v>maxime rambourg</x:v>
+      </x:c>
+      <x:c r="C80" s="34" t="str">
+        <x:v>75577</x:v>
+      </x:c>
+      <x:c r="D80" s="34" t="str">
+        <x:v>Maxime Rambourg</x:v>
+      </x:c>
+      <x:c r="E80" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/75577/maxime-rambourg</x:v>
+      </x:c>
+      <x:c r="F80" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/tVuqWE5myRJljgXeeEI9cg__previewthumb/img/dFdv5KdG3SNKBhHczOGEwhsSAPA=/fit-in/300x320/filters:strip_icc()/pic8572757.jpg</x:v>
+      </x:c>
+      <x:c r="G80" s="34" t="str">
+        <x:v>assets/designers/75577.webp</x:v>
+      </x:c>
+      <x:c r="H80" s="34" t="str">
+        <x:v>8572757</x:v>
+      </x:c>
+      <x:c r="I80" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J80" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K80" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=75577&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L80" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/472458/blood-hunt</x:v>
+      </x:c>
+      <x:c r="M80" s="34" t="str">
+        <x:v>472458</x:v>
+      </x:c>
+      <x:c r="N80" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=472458&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O80" s="34" t="str"/>
+    </x:row>
+    <x:row r="81" ht="22" customHeight="1">
+      <x:c r="A81" s="34" t="str">
+        <x:v>Maximus Laurie</x:v>
+      </x:c>
+      <x:c r="B81" s="34" t="str">
+        <x:v>maximus laurie</x:v>
+      </x:c>
+      <x:c r="C81" s="34" t="str">
+        <x:v>150711</x:v>
+      </x:c>
+      <x:c r="D81" s="34" t="str">
+        <x:v>Maximus Laurie</x:v>
+      </x:c>
+      <x:c r="E81" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/150711/maximus-laurie</x:v>
+      </x:c>
+      <x:c r="F81" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/RubiSrW9VTStdkykXRI0Sw__previewthumb/img/rMmFmriPGr7jpgjijJxqf45YXuk=/fit-in/300x320/filters:strip_icc()/pic8409147.jpg</x:v>
+      </x:c>
+      <x:c r="G81" s="34" t="str">
+        <x:v>assets/designers/150711.webp</x:v>
+      </x:c>
+      <x:c r="H81" s="34" t="str">
+        <x:v>8409147</x:v>
+      </x:c>
+      <x:c r="I81" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J81" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K81" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=150711&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L81" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/452835/andromedas-edge-genesis</x:v>
+      </x:c>
+      <x:c r="M81" s="34" t="str">
+        <x:v>452835</x:v>
+      </x:c>
+      <x:c r="N81" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=452835&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O81" s="34" t="str"/>
+    </x:row>
+    <x:row r="82" ht="22" customHeight="1">
+      <x:c r="A82" s="34" t="str">
+        <x:v>Michael Orion</x:v>
+      </x:c>
+      <x:c r="B82" s="34" t="str">
+        <x:v>michael orion</x:v>
+      </x:c>
+      <x:c r="C82" s="34" t="str">
+        <x:v>78158</x:v>
+      </x:c>
+      <x:c r="D82" s="34" t="str">
+        <x:v>Michael Orion</x:v>
+      </x:c>
+      <x:c r="E82" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/78158/michael-orion</x:v>
+      </x:c>
+      <x:c r="F82" s="34" t="str"/>
+      <x:c r="G82" s="34" t="str"/>
+      <x:c r="H82" s="34" t="str">
+        <x:v>1657690</x:v>
+      </x:c>
+      <x:c r="I82" s="34" t="str">
+        <x:v>no-image</x:v>
+      </x:c>
+      <x:c r="J82" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K82" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=78158&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L82" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/472994/stem-and-branch-spirit-scrolls</x:v>
+      </x:c>
+      <x:c r="M82" s="34" t="str">
+        <x:v>472994</x:v>
+      </x:c>
+      <x:c r="N82" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=472994&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O82" s="34" t="str">
+        <x:v>BGG 設計師個人頁使用通用缺圖圖示；BGG 個人相簿查核：圖庫無圖片；相簿來源：https://api.geekdo.com/api/images?ajax=1&amp;gallery=all&amp;nosession=1&amp;objectid=78158&amp;objecttype=person&amp;pageid=1&amp;showcount=10&amp;sort=hot</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" ht="22" customHeight="1">
+      <x:c r="A83" s="34" t="str">
+        <x:v>Michael Rieneck</x:v>
+      </x:c>
+      <x:c r="B83" s="34" t="str">
+        <x:v>michael rieneck</x:v>
+      </x:c>
+      <x:c r="C83" s="34" t="str">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="D83" s="34" t="str">
+        <x:v>Michael Rieneck</x:v>
+      </x:c>
+      <x:c r="E83" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/142/michael-rieneck</x:v>
+      </x:c>
+      <x:c r="F83" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/elyTJj4W5Ymn2o-7ubmD_A__previewthumb/img/EVthURpAVwZLG4fd7C3PdFRCNL4=/fit-in/300x320/filters:strip_icc()/pic498492.jpg</x:v>
+      </x:c>
+      <x:c r="G83" s="34" t="str">
+        <x:v>assets/designers/142.webp</x:v>
+      </x:c>
+      <x:c r="H83" s="34" t="str">
+        <x:v>498492</x:v>
+      </x:c>
+      <x:c r="I83" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J83" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K83" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=142&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L83" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/64461/cuba-kanadische-botschaft</x:v>
+      </x:c>
+      <x:c r="M83" s="34" t="str">
+        <x:v>64461</x:v>
+      </x:c>
+      <x:c r="N83" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=64461&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O83" s="34" t="str"/>
+    </x:row>
+    <x:row r="84" ht="22" customHeight="1">
+      <x:c r="A84" s="34" t="str">
+        <x:v>Milan Tasevski</x:v>
+      </x:c>
+      <x:c r="B84" s="34" t="str">
+        <x:v>milan tasevski</x:v>
+      </x:c>
+      <x:c r="C84" s="34" t="str">
+        <x:v>82565</x:v>
+      </x:c>
+      <x:c r="D84" s="34" t="str">
+        <x:v>Milan Tasevski</x:v>
+      </x:c>
+      <x:c r="E84" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/82565/milan-tasevski</x:v>
+      </x:c>
+      <x:c r="F84" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/_R4JNzw0WRPg9VmZfjJPPQ__previewthumb/img/i0oJHiQv7Hu75TF8XjFxHTjXVm0=/fit-in/300x320/filters:strip_icc()/pic3231829.jpg</x:v>
+      </x:c>
+      <x:c r="G84" s="34" t="str">
+        <x:v>assets/designers/82565.webp</x:v>
+      </x:c>
+      <x:c r="H84" s="34" t="str">
+        <x:v>3231829</x:v>
+      </x:c>
+      <x:c r="I84" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J84" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K84" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=82565&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L84" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/445034/light-in-the-dark-fires-of-thokaia</x:v>
+      </x:c>
+      <x:c r="M84" s="34" t="str">
+        <x:v>445034</x:v>
+      </x:c>
+      <x:c r="N84" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=445034&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O84" s="34" t="str"/>
+    </x:row>
+    <x:row r="85" ht="22" customHeight="1">
+      <x:c r="A85" s="34" t="str">
+        <x:v>Mín</x:v>
+      </x:c>
+      <x:c r="B85" s="34" t="str">
+        <x:v>mín</x:v>
+      </x:c>
+      <x:c r="C85" s="34" t="str">
+        <x:v>127822</x:v>
+      </x:c>
+      <x:c r="D85" s="34" t="str">
+        <x:v>Mín</x:v>
+      </x:c>
+      <x:c r="E85" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/127822/min</x:v>
+      </x:c>
+      <x:c r="F85" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/1CjeqtF_PKoRGMuuy1ZvPw__previewthumb/img/30d7Q_Zi-uZJ7yq3EFWVIZpVcSI=/fit-in/300x320/filters:strip_icc()/pic5533931.jpg</x:v>
+      </x:c>
+      <x:c r="G85" s="34" t="str">
+        <x:v>assets/designers/127822.webp</x:v>
+      </x:c>
+      <x:c r="H85" s="34" t="str">
+        <x:v>5533931</x:v>
+      </x:c>
+      <x:c r="I85" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J85" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K85" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=127822&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L85" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/475207/lost-ruins-of-arnak-surprise-shipment</x:v>
+      </x:c>
+      <x:c r="M85" s="34" t="str">
+        <x:v>475207</x:v>
+      </x:c>
+      <x:c r="N85" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=475207&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O85" s="34" t="str"/>
+    </x:row>
+    <x:row r="86" ht="22" customHeight="1">
+      <x:c r="A86" s="34" t="str">
+        <x:v>Nicolas Oury</x:v>
+      </x:c>
+      <x:c r="B86" s="34" t="str">
+        <x:v>nicolas oury</x:v>
+      </x:c>
+      <x:c r="C86" s="34" t="str">
+        <x:v>6475</x:v>
+      </x:c>
+      <x:c r="D86" s="34" t="str">
+        <x:v>Nicolas Oury</x:v>
+      </x:c>
+      <x:c r="E86" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/6475/nicolas-oury</x:v>
+      </x:c>
+      <x:c r="F86" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/AtgYHIVXF_m8fOk-3QtvDg__previewthumb/img/KLVumT1CcZUse0OSsftWjyNs8MQ=/fit-in/300x320/filters:strip_icc()/pic121478.jpg</x:v>
+      </x:c>
+      <x:c r="G86" s="34" t="str">
+        <x:v>assets/designers/6475.webp</x:v>
+      </x:c>
+      <x:c r="H86" s="34" t="str">
+        <x:v>121478</x:v>
+      </x:c>
+      <x:c r="I86" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J86" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K86" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=6475&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L86" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/473010/mykerinos-special-edition</x:v>
+      </x:c>
+      <x:c r="M86" s="34" t="str">
+        <x:v>473010</x:v>
+      </x:c>
+      <x:c r="N86" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=473010&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O86" s="34" t="str"/>
+    </x:row>
+    <x:row r="87" ht="22" customHeight="1">
+      <x:c r="A87" s="34" t="str">
+        <x:v>Nigel Buckle</x:v>
+      </x:c>
+      <x:c r="B87" s="34" t="str">
+        <x:v>nigel buckle</x:v>
+      </x:c>
+      <x:c r="C87" s="34" t="str">
+        <x:v>5864</x:v>
+      </x:c>
+      <x:c r="D87" s="34" t="str">
+        <x:v>Nigel Buckle</x:v>
+      </x:c>
+      <x:c r="E87" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/5864/nigel-buckle</x:v>
+      </x:c>
+      <x:c r="F87" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/wm4TJhkbgBGS92zouo6Kcw__previewthumb/img/lnFieiTG11aYQjTfOXv9v4G9FWA=/fit-in/300x320/filters:strip_icc()/pic744451.jpg</x:v>
+      </x:c>
+      <x:c r="G87" s="34" t="str">
+        <x:v>assets/designers/5864.webp</x:v>
+      </x:c>
+      <x:c r="H87" s="34" t="str">
+        <x:v>744451</x:v>
+      </x:c>
+      <x:c r="I87" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J87" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K87" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=5864&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L87" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/455819/voidfall-resurgence</x:v>
+      </x:c>
+      <x:c r="M87" s="34" t="str">
+        <x:v>455819</x:v>
+      </x:c>
+      <x:c r="N87" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=455819&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O87" s="34" t="str"/>
+    </x:row>
+    <x:row r="88" ht="22" customHeight="1">
+      <x:c r="A88" s="34" t="str">
+        <x:v>Oleg Meleshin</x:v>
+      </x:c>
+      <x:c r="B88" s="34" t="str">
+        <x:v>oleg meleshin</x:v>
+      </x:c>
+      <x:c r="C88" s="34" t="str">
+        <x:v>122916</x:v>
+      </x:c>
+      <x:c r="D88" s="34" t="str">
+        <x:v>Oleg Meleshin</x:v>
+      </x:c>
+      <x:c r="E88" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/122916/oleg-meleshin</x:v>
+      </x:c>
+      <x:c r="F88" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/qigN2znRJ-uKb-HkIJQeLg__previewthumb/img/Dv_ndIJGwW09LAfanYVSlz7bs8g=/fit-in/300x320/filters:strip_icc()/pic8538529.jpg</x:v>
+      </x:c>
+      <x:c r="G88" s="34" t="str">
+        <x:v>assets/designers/122916.webp</x:v>
+      </x:c>
+      <x:c r="H88" s="34" t="str">
+        <x:v>8538529</x:v>
+      </x:c>
+      <x:c r="I88" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J88" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K88" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=122916&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L88" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/475943/sweepers</x:v>
+      </x:c>
+      <x:c r="M88" s="34" t="str">
+        <x:v>475943</x:v>
+      </x:c>
+      <x:c r="N88" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=475943&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O88" s="34" t="str"/>
+    </x:row>
+    <x:row r="89" ht="22" customHeight="1">
+      <x:c r="A89" s="34" t="str">
+        <x:v>Orin Bishop</x:v>
+      </x:c>
+      <x:c r="B89" s="34" t="str">
+        <x:v>orin bishop</x:v>
+      </x:c>
+      <x:c r="C89" s="34" t="str">
+        <x:v>76528</x:v>
+      </x:c>
+      <x:c r="D89" s="34" t="str">
+        <x:v>Orin Bishop</x:v>
+      </x:c>
+      <x:c r="E89" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/76528/orin-bishop</x:v>
+      </x:c>
+      <x:c r="F89" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/mg4Uv_gnqHd6IgNPWnPGsQ__previewthumb/img/dqj0LyTOzBE2kutZDLB2vMmtz34=/fit-in/300x320/filters:strip_icc()/pic2074260.png</x:v>
+      </x:c>
+      <x:c r="G89" s="34" t="str">
+        <x:v>assets/designers/76528.webp</x:v>
+      </x:c>
+      <x:c r="H89" s="34" t="str">
+        <x:v>2074260</x:v>
+      </x:c>
+      <x:c r="I89" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J89" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K89" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=76528&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L89" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/162007/steampunk-rally</x:v>
+      </x:c>
+      <x:c r="M89" s="34" t="str">
+        <x:v>162007</x:v>
+      </x:c>
+      <x:c r="N89" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=162007&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O89" s="34" t="str"/>
+    </x:row>
+    <x:row r="90" ht="22" customHeight="1">
+      <x:c r="A90" s="34" t="str">
+        <x:v>Paul Dennen</x:v>
+      </x:c>
+      <x:c r="B90" s="34" t="str">
+        <x:v>paul dennen</x:v>
+      </x:c>
+      <x:c r="C90" s="34" t="str">
+        <x:v>92370</x:v>
+      </x:c>
+      <x:c r="D90" s="34" t="str">
+        <x:v>Paul Dennen</x:v>
+      </x:c>
+      <x:c r="E90" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/92370/paul-dennen</x:v>
+      </x:c>
+      <x:c r="F90" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/Fif1H8whCgtWMNg0OnsEPg__previewthumb/img/5VwnOCm_6V7lPw6vQmBMLsPJvC4=/fit-in/300x320/filters:strip_icc()/pic8364523.jpg</x:v>
+      </x:c>
+      <x:c r="G90" s="34" t="str">
+        <x:v>assets/designers/92370.webp</x:v>
+      </x:c>
+      <x:c r="H90" s="34" t="str">
+        <x:v>8364523</x:v>
+      </x:c>
+      <x:c r="I90" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J90" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K90" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=92370&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L90" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/426129/dune-imperium-bloodlines</x:v>
+      </x:c>
+      <x:c r="M90" s="34" t="str">
+        <x:v>426129</x:v>
+      </x:c>
+      <x:c r="N90" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=426129&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O90" s="34" t="str"/>
+    </x:row>
+    <x:row r="91" ht="22" customHeight="1">
+      <x:c r="A91" s="34" t="str">
+        <x:v>Phil Amylon</x:v>
+      </x:c>
+      <x:c r="B91" s="34" t="str">
+        <x:v>phil amylon</x:v>
+      </x:c>
+      <x:c r="C91" s="34" t="str">
+        <x:v>104307</x:v>
+      </x:c>
+      <x:c r="D91" s="34" t="str">
+        <x:v>Phil Amylon</x:v>
+      </x:c>
+      <x:c r="E91" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/104307/phil-amylon</x:v>
+      </x:c>
+      <x:c r="F91" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/aljQL2xGPj8e8H8f9lLNvQ__previewthumb/img/jwcR1Q0wkDIQzH60m1Xy7a2Fu7U=/fit-in/300x320/filters:strip_icc()/pic8364489.jpg</x:v>
+      </x:c>
+      <x:c r="G91" s="34" t="str">
+        <x:v>assets/designers/104307.webp</x:v>
+      </x:c>
+      <x:c r="H91" s="34" t="str">
+        <x:v>8364489</x:v>
+      </x:c>
+      <x:c r="I91" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J91" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K91" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=104307&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L91" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/426129/dune-imperium-bloodlines</x:v>
+      </x:c>
+      <x:c r="M91" s="34" t="str">
+        <x:v>426129</x:v>
+      </x:c>
+      <x:c r="N91" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=426129&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O91" s="34" t="str"/>
+    </x:row>
+    <x:row r="92" ht="22" customHeight="1">
+      <x:c r="A92" s="34" t="str">
+        <x:v>Pierrot</x:v>
+      </x:c>
+      <x:c r="B92" s="34" t="str">
+        <x:v>pierrot</x:v>
+      </x:c>
+      <x:c r="C92" s="34" t="str">
+        <x:v>97077</x:v>
+      </x:c>
+      <x:c r="D92" s="34" t="str">
+        <x:v>Pierrot</x:v>
+      </x:c>
+      <x:c r="E92" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/97077/pierrot</x:v>
+      </x:c>
+      <x:c r="F92" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/05BLFbr8cdMKXZcQUXIy2w__previewthumb/img/zMyu6UB9yhdQ_J6ZJz6yqT6BptQ=/fit-in/300x320/filters:strip_icc()/pic4339973.jpg</x:v>
+      </x:c>
+      <x:c r="G92" s="34" t="str">
+        <x:v>assets/designers/97077.webp</x:v>
+      </x:c>
+      <x:c r="H92" s="34" t="str">
+        <x:v>4339973</x:v>
+      </x:c>
+      <x:c r="I92" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J92" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K92" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=97077&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L92" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/405542/caravanserai</x:v>
+      </x:c>
+      <x:c r="M92" s="34" t="str">
+        <x:v>405542</x:v>
+      </x:c>
+      <x:c r="N92" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=405542&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O92" s="34" t="str"/>
+    </x:row>
+    <x:row r="93" ht="22" customHeight="1">
+      <x:c r="A93" s="34" t="str">
+        <x:v>Raymond Chandler III</x:v>
+      </x:c>
+      <x:c r="B93" s="34" t="str">
+        <x:v>raymond chandler iii</x:v>
+      </x:c>
+      <x:c r="C93" s="34" t="str">
+        <x:v>79057</x:v>
+      </x:c>
+      <x:c r="D93" s="34" t="str">
+        <x:v>Raymond Chandler III</x:v>
+      </x:c>
+      <x:c r="E93" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/79057/raymond-chandler-iii</x:v>
+      </x:c>
+      <x:c r="F93" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/2HVjWgmFPafaTQ4QD2Wmag__previewthumb/img/vjr0ZOBjRbM-Z6QzEFCHxEBuUMs=/fit-in/300x320/filters:strip_icc()/pic3161430.jpg</x:v>
+      </x:c>
+      <x:c r="G93" s="34" t="str">
+        <x:v>assets/designers/79057.webp</x:v>
+      </x:c>
+      <x:c r="H93" s="34" t="str">
+        <x:v>3161430</x:v>
+      </x:c>
+      <x:c r="I93" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J93" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K93" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=79057&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L93" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/214880/chicago-1875-city-of-the-big-shoulders</x:v>
+      </x:c>
+      <x:c r="M93" s="34" t="str">
+        <x:v>214880</x:v>
+      </x:c>
+      <x:c r="N93" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=214880&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O93" s="34" t="str"/>
+    </x:row>
+    <x:row r="94" ht="22" customHeight="1">
+      <x:c r="A94" s="34" t="str">
+        <x:v>Reiner Knizia</x:v>
+      </x:c>
+      <x:c r="B94" s="34" t="str">
+        <x:v>reiner knizia</x:v>
+      </x:c>
+      <x:c r="C94" s="34" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D94" s="34" t="str">
+        <x:v>Reiner Knizia</x:v>
+      </x:c>
+      <x:c r="E94" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/2/reiner-knizia</x:v>
+      </x:c>
+      <x:c r="F94" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/shDlOkQued8T1R6cDNJuKg__previewthumb/img/x84QigdoCIIyw_qQLdQrDuT0T-0=/fit-in/300x320/filters:strip_icc()/pic9061128.png</x:v>
+      </x:c>
+      <x:c r="G94" s="34" t="str">
+        <x:v>assets/designers/2.webp</x:v>
+      </x:c>
+      <x:c r="H94" s="34" t="str">
+        <x:v>9061128</x:v>
+      </x:c>
+      <x:c r="I94" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J94" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K94" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=2&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L94" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/18833/the-lord-of-the-rings-the-confrontation</x:v>
+      </x:c>
+      <x:c r="M94" s="34" t="str">
+        <x:v>18833</x:v>
+      </x:c>
+      <x:c r="N94" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=18833&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O94" s="34" t="str"/>
+    </x:row>
+    <x:row r="95" ht="22" customHeight="1">
+      <x:c r="A95" s="34" t="str">
+        <x:v>Reiner Stockhausen</x:v>
+      </x:c>
+      <x:c r="B95" s="34" t="str">
+        <x:v>reiner stockhausen</x:v>
+      </x:c>
+      <x:c r="C95" s="34" t="str">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="D95" s="34" t="str">
+        <x:v>Reiner Stockhausen</x:v>
+      </x:c>
+      <x:c r="E95" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/158/reiner-stockhausen</x:v>
+      </x:c>
+      <x:c r="F95" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/vxLLH2y7CtcNqOEgVFTYUg__previewthumb/img/zZ56YXPXMu_P8GW1VoTnuGET4zs=/fit-in/300x320/filters:strip_icc()/pic993538.png</x:v>
+      </x:c>
+      <x:c r="G95" s="34" t="str">
+        <x:v>assets/designers/158.webp</x:v>
+      </x:c>
+      <x:c r="H95" s="34" t="str">
+        <x:v>993538</x:v>
+      </x:c>
+      <x:c r="I95" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J95" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K95" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=158&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L95" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/171905/orleans-deluxe-edition</x:v>
+      </x:c>
+      <x:c r="M95" s="34" t="str">
+        <x:v>171905</x:v>
+      </x:c>
+      <x:c r="N95" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=171905&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O95" s="34" t="str"/>
+    </x:row>
+    <x:row r="96" ht="22" customHeight="1">
+      <x:c r="A96" s="34" t="str">
+        <x:v>Richard Ámann</x:v>
+      </x:c>
+      <x:c r="B96" s="34" t="str">
+        <x:v>richard ámann</x:v>
+      </x:c>
+      <x:c r="C96" s="34" t="str">
+        <x:v>76971</x:v>
+      </x:c>
+      <x:c r="D96" s="34" t="str">
+        <x:v>Richard Ámann</x:v>
+      </x:c>
+      <x:c r="E96" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/76971/richard-amann</x:v>
+      </x:c>
+      <x:c r="F96" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/q961h83W57w5oLcPtGusZA__previewthumb/img/dX0DmPwf_kDZ1emWmujxaNvyANA=/fit-in/300x320/filters:strip_icc()/pic8641925.jpg</x:v>
+      </x:c>
+      <x:c r="G96" s="34" t="str">
+        <x:v>assets/designers/76971.webp</x:v>
+      </x:c>
+      <x:c r="H96" s="34" t="str">
+        <x:v>8641925</x:v>
+      </x:c>
+      <x:c r="I96" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J96" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K96" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=76971&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L96" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/256997/perseverance-castaway-chronicles-episodes-1-and-2</x:v>
+      </x:c>
+      <x:c r="M96" s="34" t="str">
+        <x:v>256997</x:v>
+      </x:c>
+      <x:c r="N96" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=256997&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O96" s="34" t="str"/>
+    </x:row>
+    <x:row r="97" ht="22" customHeight="1">
+      <x:c r="A97" s="34" t="str">
+        <x:v>Robert Hovakimyan</x:v>
+      </x:c>
+      <x:c r="B97" s="34" t="str">
+        <x:v>robert hovakimyan</x:v>
+      </x:c>
+      <x:c r="C97" s="34" t="str">
+        <x:v>157655</x:v>
+      </x:c>
+      <x:c r="D97" s="34" t="str">
+        <x:v>Robert Hovakimyan</x:v>
+      </x:c>
+      <x:c r="E97" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/157655/robert-hovakimyan</x:v>
+      </x:c>
+      <x:c r="F97" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/Atv42Zggl8TCF2WMn4nF4Q__previewthumb/img/cADheKXmXsplv6dM1iQEBVym7bE=/fit-in/300x320/filters:strip_icc()/pic7846702.jpg</x:v>
+      </x:c>
+      <x:c r="G97" s="34" t="str">
+        <x:v>assets/designers/157655.webp</x:v>
+      </x:c>
+      <x:c r="H97" s="34" t="str">
+        <x:v>7846702</x:v>
+      </x:c>
+      <x:c r="I97" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J97" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K97" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=157655&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L97" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/465889/arribada</x:v>
+      </x:c>
+      <x:c r="M97" s="34" t="str">
+        <x:v>465889</x:v>
+      </x:c>
+      <x:c r="N97" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=465889&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O97" s="34" t="str"/>
+    </x:row>
+    <x:row r="98" ht="22" customHeight="1">
+      <x:c r="A98" s="34" t="str">
+        <x:v>Robert Laing</x:v>
+      </x:c>
+      <x:c r="B98" s="34" t="str">
+        <x:v>robert laing</x:v>
+      </x:c>
+      <x:c r="C98" s="34" t="str">
+        <x:v>6554</x:v>
+      </x:c>
+      <x:c r="D98" s="34" t="str">
+        <x:v>Robert Laing</x:v>
+      </x:c>
+      <x:c r="E98" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/6554/robert-laing</x:v>
+      </x:c>
+      <x:c r="F98" s="34" t="str"/>
+      <x:c r="G98" s="34" t="str"/>
+      <x:c r="H98" s="34" t="str">
+        <x:v>1657690</x:v>
+      </x:c>
+      <x:c r="I98" s="34" t="str">
+        <x:v>no-image</x:v>
+      </x:c>
+      <x:c r="J98" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K98" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=6554&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L98" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/462713/the-anarchy</x:v>
+      </x:c>
+      <x:c r="M98" s="34" t="str">
+        <x:v>462713</x:v>
+      </x:c>
+      <x:c r="N98" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=462713&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O98" s="34" t="str">
+        <x:v>BGG 設計師個人頁使用通用缺圖圖示；BGG 個人相簿查核：圖庫無圖片；相簿來源：https://api.geekdo.com/api/images?ajax=1&amp;gallery=all&amp;nosession=1&amp;objectid=6554&amp;objecttype=person&amp;pageid=1&amp;showcount=10&amp;sort=hot</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" ht="22" customHeight="1">
+      <x:c r="A99" s="34" t="str">
+        <x:v>Roman Bednář</x:v>
+      </x:c>
+      <x:c r="B99" s="34" t="str">
+        <x:v>roman bednář</x:v>
+      </x:c>
+      <x:c r="C99" s="34" t="str">
+        <x:v>152612</x:v>
+      </x:c>
+      <x:c r="D99" s="34" t="str">
+        <x:v>Roman Bednář</x:v>
+      </x:c>
+      <x:c r="E99" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/152612/roman-bednar</x:v>
+      </x:c>
+      <x:c r="F99" s="34" t="str"/>
+      <x:c r="G99" s="34" t="str"/>
+      <x:c r="H99" s="34" t="str">
+        <x:v>1657690</x:v>
+      </x:c>
+      <x:c r="I99" s="34" t="str">
+        <x:v>no-image</x:v>
+      </x:c>
+      <x:c r="J99" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K99" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=152612&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L99" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/465669/drillers</x:v>
+      </x:c>
+      <x:c r="M99" s="34" t="str">
+        <x:v>465669</x:v>
+      </x:c>
+      <x:c r="N99" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=465669&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O99" s="34" t="str">
+        <x:v>BGG 設計師個人頁使用通用缺圖圖示；BGG 個人相簿查核：圖庫無圖片；相簿來源：https://api.geekdo.com/api/images?ajax=1&amp;gallery=all&amp;nosession=1&amp;objectid=152612&amp;objecttype=person&amp;pageid=1&amp;showcount=10&amp;sort=hot</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" ht="22" customHeight="1">
+      <x:c r="A100" s="34" t="str">
+        <x:v>Roy Cannaday</x:v>
+      </x:c>
+      <x:c r="B100" s="34" t="str">
+        <x:v>roy cannaday</x:v>
+      </x:c>
+      <x:c r="C100" s="34" t="str">
+        <x:v>59359</x:v>
+      </x:c>
+      <x:c r="D100" s="34" t="str">
+        <x:v>Roy Cannaday</x:v>
+      </x:c>
+      <x:c r="E100" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/59359/roy-cannaday</x:v>
+      </x:c>
+      <x:c r="F100" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/j2UuZL5DHDWzwFKhTyP0wA__previewthumb/img/3WubGdVwgvzsTlnjkz3uU13ny6U=/fit-in/300x320/filters:strip_icc()/pic6784733.jpg</x:v>
+      </x:c>
+      <x:c r="G100" s="34" t="str">
+        <x:v>assets/designers/59359.webp</x:v>
+      </x:c>
+      <x:c r="H100" s="34" t="str">
+        <x:v>6784733</x:v>
+      </x:c>
+      <x:c r="I100" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J100" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K100" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=59359&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L100" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/315727/last-light</x:v>
+      </x:c>
+      <x:c r="M100" s="34" t="str">
+        <x:v>315727</x:v>
+      </x:c>
+      <x:c r="N100" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=315727&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O100" s="34" t="str"/>
+    </x:row>
+    <x:row r="101" ht="22" customHeight="1">
+      <x:c r="A101" s="34" t="str">
+        <x:v>Ruth Veevers</x:v>
+      </x:c>
+      <x:c r="B101" s="34" t="str">
+        <x:v>ruth veevers</x:v>
+      </x:c>
+      <x:c r="C101" s="34" t="str">
+        <x:v>107036</x:v>
+      </x:c>
+      <x:c r="D101" s="34" t="str">
+        <x:v>Ruth Veevers</x:v>
+      </x:c>
+      <x:c r="E101" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/107036/ruth-veevers</x:v>
+      </x:c>
+      <x:c r="F101" s="34" t="str"/>
+      <x:c r="G101" s="34" t="str"/>
+      <x:c r="H101" s="34" t="str">
+        <x:v>1657690</x:v>
+      </x:c>
+      <x:c r="I101" s="34" t="str">
+        <x:v>no-image</x:v>
+      </x:c>
+      <x:c r="J101" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K101" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=107036&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L101" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/343274/cryptid-urban-legends</x:v>
+      </x:c>
+      <x:c r="M101" s="34" t="str">
+        <x:v>343274</x:v>
+      </x:c>
+      <x:c r="N101" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=343274&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O101" s="34" t="str">
+        <x:v>BGG 設計師個人頁使用通用缺圖圖示；BGG 個人相簿查核：圖庫無圖片；相簿來源：https://api.geekdo.com/api/images?ajax=1&amp;gallery=all&amp;nosession=1&amp;objectid=107036&amp;objecttype=person&amp;pageid=1&amp;showcount=10&amp;sort=hot</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" ht="22" customHeight="1">
+      <x:c r="A102" s="34" t="str">
+        <x:v>Rémi Mathieu</x:v>
+      </x:c>
+      <x:c r="B102" s="34" t="str">
+        <x:v>rémi mathieu</x:v>
+      </x:c>
+      <x:c r="C102" s="34" t="str">
+        <x:v>136845</x:v>
+      </x:c>
+      <x:c r="D102" s="34" t="str">
+        <x:v>Rémi Mathieu</x:v>
+      </x:c>
+      <x:c r="E102" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/136845/remi-mathieu</x:v>
+      </x:c>
+      <x:c r="F102" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/0yzw0_I1SBXda1UEaggyFg__previewthumb/img/YQ0gPvy_c5KrUvzz5NocfEi8ARw=/fit-in/300x320/filters:strip_icc()/pic7770156.jpg</x:v>
+      </x:c>
+      <x:c r="G102" s="34" t="str">
+        <x:v>assets/designers/136845.webp</x:v>
+      </x:c>
+      <x:c r="H102" s="34" t="str">
+        <x:v>7770156</x:v>
+      </x:c>
+      <x:c r="I102" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J102" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K102" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=136845&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L102" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/423309/arctica</x:v>
+      </x:c>
+      <x:c r="M102" s="34" t="str">
+        <x:v>423309</x:v>
+      </x:c>
+      <x:c r="N102" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=423309&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O102" s="34" t="str"/>
+    </x:row>
+    <x:row r="103" ht="22" customHeight="1">
+      <x:c r="A103" s="34" t="str">
+        <x:v>S J Macdonald</x:v>
+      </x:c>
+      <x:c r="B103" s="34" t="str">
+        <x:v>s j macdonald</x:v>
+      </x:c>
+      <x:c r="C103" s="34" t="str">
+        <x:v>103821</x:v>
+      </x:c>
+      <x:c r="D103" s="34" t="str">
+        <x:v>S J Macdonald</x:v>
+      </x:c>
+      <x:c r="E103" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/103821/s-j-macdonald</x:v>
+      </x:c>
+      <x:c r="F103" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/m2Ha8orEfodALLg0Ydttgw__previewthumb/img/cAaj5T5z4S4cPkONAGNqwQbg18g=/fit-in/300x320/filters:strip_icc()/pic4412892.jpg</x:v>
+      </x:c>
+      <x:c r="G103" s="34" t="str">
+        <x:v>assets/designers/103821.webp</x:v>
+      </x:c>
+      <x:c r="H103" s="34" t="str">
+        <x:v>4412892</x:v>
+      </x:c>
+      <x:c r="I103" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J103" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K103" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=103821&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L103" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/432067/assyria-second-edition</x:v>
+      </x:c>
+      <x:c r="M103" s="34" t="str">
+        <x:v>432067</x:v>
+      </x:c>
+      <x:c r="N103" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=432067&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O103" s="34" t="str"/>
+    </x:row>
+    <x:row r="104" ht="22" customHeight="1">
+      <x:c r="A104" s="34" t="str">
+        <x:v>Sams</x:v>
+      </x:c>
+      <x:c r="B104" s="34" t="str">
+        <x:v>sams</x:v>
+      </x:c>
+      <x:c r="C104" s="34" t="str">
+        <x:v>125940</x:v>
+      </x:c>
+      <x:c r="D104" s="34" t="str">
+        <x:v>Sams</x:v>
+      </x:c>
+      <x:c r="E104" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/125940/sams</x:v>
+      </x:c>
+      <x:c r="F104" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/m3b3EwtAz2xBosG8vNyvzQ__previewthumb/img/-9VaHOsPYKwjDGRN1CWW4zPzV-w=/fit-in/300x320/filters:strip_icc()/pic5331818.jpg</x:v>
+      </x:c>
+      <x:c r="G104" s="34" t="str">
+        <x:v>assets/designers/125940.webp</x:v>
+      </x:c>
+      <x:c r="H104" s="34" t="str">
+        <x:v>5331818</x:v>
+      </x:c>
+      <x:c r="I104" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J104" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K104" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=125940&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L104" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/423309/arctica</x:v>
+      </x:c>
+      <x:c r="M104" s="34" t="str">
+        <x:v>423309</x:v>
+      </x:c>
+      <x:c r="N104" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=423309&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O104" s="34" t="str"/>
+    </x:row>
+    <x:row r="105" ht="22" customHeight="1">
+      <x:c r="A105" s="34" t="str">
+        <x:v>Samuele Sai</x:v>
+      </x:c>
+      <x:c r="B105" s="34" t="str">
+        <x:v>samuele sai</x:v>
+      </x:c>
+      <x:c r="C105" s="34" t="str">
+        <x:v>83891</x:v>
+      </x:c>
+      <x:c r="D105" s="34" t="str">
+        <x:v>Samuele Sai</x:v>
+      </x:c>
+      <x:c r="E105" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/83891/samuele-sai</x:v>
+      </x:c>
+      <x:c r="F105" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/j-DqKRajmO3zksYXgdjbmQ__previewthumb/img/6KLHwh4eYNCFOcu2LSDHS2XeOS8=/fit-in/300x320/filters:strip_icc()/pic3903255.jpg</x:v>
+      </x:c>
+      <x:c r="G105" s="34" t="str">
+        <x:v>assets/designers/83891.webp</x:v>
+      </x:c>
+      <x:c r="H105" s="34" t="str">
+        <x:v>3903255</x:v>
+      </x:c>
+      <x:c r="I105" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J105" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K105" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=83891&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L105" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/224664/la-famiglia</x:v>
+      </x:c>
+      <x:c r="M105" s="34" t="str">
+        <x:v>224664</x:v>
+      </x:c>
+      <x:c r="N105" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=224664&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O105" s="34" t="str"/>
+    </x:row>
+    <x:row r="106" ht="22" customHeight="1">
+      <x:c r="A106" s="34" t="str">
+        <x:v>Sarah Joshua</x:v>
+      </x:c>
+      <x:c r="B106" s="34" t="str">
+        <x:v>sarah joshua</x:v>
+      </x:c>
+      <x:c r="C106" s="34" t="str">
+        <x:v>172830</x:v>
+      </x:c>
+      <x:c r="D106" s="34" t="str">
+        <x:v>Sarah Joshua</x:v>
+      </x:c>
+      <x:c r="E106" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/172830/sarah-joshua</x:v>
+      </x:c>
+      <x:c r="F106" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/FrMFCH3y0KBvLcaFInZgEQ__previewthumb/img/HEgFFU10NHXI2Qd8mhZOuvp3dQY=/fit-in/300x320/filters:strip_icc()/pic9334903.jpg</x:v>
+      </x:c>
+      <x:c r="G106" s="34" t="str">
+        <x:v>assets/designers/172830.webp</x:v>
+      </x:c>
+      <x:c r="H106" s="34" t="str">
+        <x:v>9334903</x:v>
+      </x:c>
+      <x:c r="I106" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J106" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K106" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=172830&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L106" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/477997/enchanted-ivy-gamemasters-challenge</x:v>
+      </x:c>
+      <x:c r="M106" s="34" t="str">
+        <x:v>477997</x:v>
+      </x:c>
+      <x:c r="N106" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=477997&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O106" s="34" t="str"/>
+    </x:row>
+    <x:row r="107" ht="22" customHeight="1">
+      <x:c r="A107" s="34" t="str">
+        <x:v>Seth Van Orden</x:v>
+      </x:c>
+      <x:c r="B107" s="34" t="str">
+        <x:v>seth van orden</x:v>
+      </x:c>
+      <x:c r="C107" s="34" t="str">
+        <x:v>76233</x:v>
+      </x:c>
+      <x:c r="D107" s="34" t="str">
+        <x:v>Seth Van Orden</x:v>
+      </x:c>
+      <x:c r="E107" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/76233/seth-van-orden</x:v>
+      </x:c>
+      <x:c r="F107" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/V8sBN6ZohZjOgxRpNc-vfg__previewthumb/img/crAN_nSiGssfJFj91TZigcBK9Hk=/fit-in/300x320/filters:strip_icc()/pic2199038.jpg</x:v>
+      </x:c>
+      <x:c r="G107" s="34" t="str">
+        <x:v>assets/designers/76233.webp</x:v>
+      </x:c>
+      <x:c r="H107" s="34" t="str">
+        <x:v>2199038</x:v>
+      </x:c>
+      <x:c r="I107" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J107" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K107" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=76233&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L107" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/208024/reckoners</x:v>
+      </x:c>
+      <x:c r="M107" s="34" t="str">
+        <x:v>208024</x:v>
+      </x:c>
+      <x:c r="N107" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=208024&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O107" s="34" t="str"/>
+    </x:row>
+    <x:row r="108" ht="22" customHeight="1">
+      <x:c r="A108" s="34" t="str">
+        <x:v>Shem Phillips</x:v>
+      </x:c>
+      <x:c r="B108" s="34" t="str">
+        <x:v>shem phillips</x:v>
+      </x:c>
+      <x:c r="C108" s="34" t="str">
+        <x:v>12547</x:v>
+      </x:c>
+      <x:c r="D108" s="34" t="str">
+        <x:v>Shem Phillips</x:v>
+      </x:c>
+      <x:c r="E108" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/12547/shem-phillips</x:v>
+      </x:c>
+      <x:c r="F108" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/qsyJe_YMaIvhrvySBz_OIQ__previewthumb/img/6OI-RUGdIuz5pbDT_Ut-tAGdJN0=/fit-in/300x320/filters:strip_icc()/pic7612892.jpg</x:v>
+      </x:c>
+      <x:c r="G108" s="34" t="str">
+        <x:v>assets/designers/12547.webp</x:v>
+      </x:c>
+      <x:c r="H108" s="34" t="str">
+        <x:v>7612892</x:v>
+      </x:c>
+      <x:c r="I108" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J108" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K108" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=12547&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L108" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/432067/assyria-second-edition</x:v>
+      </x:c>
+      <x:c r="M108" s="34" t="str">
+        <x:v>432067</x:v>
+      </x:c>
+      <x:c r="N108" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=432067&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O108" s="34" t="str"/>
+    </x:row>
+    <x:row r="109" ht="22" customHeight="1">
+      <x:c r="A109" s="34" t="str">
+        <x:v>Simon Milburn</x:v>
+      </x:c>
+      <x:c r="B109" s="34" t="str">
+        <x:v>simon milburn</x:v>
+      </x:c>
+      <x:c r="C109" s="34" t="str">
+        <x:v>105302</x:v>
+      </x:c>
+      <x:c r="D109" s="34" t="str">
+        <x:v>Simon Milburn</x:v>
+      </x:c>
+      <x:c r="E109" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/105302/simon-milburn</x:v>
+      </x:c>
+      <x:c r="F109" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/R6mw3Ld0wNq8FdGwh14ksA__previewthumb/img/mWTcZT7M5niZRBuy4jIGFlHK0Po=/fit-in/300x320/filters:strip_icc()/pic7306970.jpg</x:v>
+      </x:c>
+      <x:c r="G109" s="34" t="str">
+        <x:v>assets/designers/105302.webp</x:v>
+      </x:c>
+      <x:c r="H109" s="34" t="str">
+        <x:v>7306970</x:v>
+      </x:c>
+      <x:c r="I109" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J109" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K109" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=105302&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L109" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/452132/jackpot-set-the-reel-expansions</x:v>
+      </x:c>
+      <x:c r="M109" s="34" t="str">
+        <x:v>452132</x:v>
+      </x:c>
+      <x:c r="N109" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=452132&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O109" s="34" t="str"/>
+    </x:row>
+    <x:row r="110" ht="22" customHeight="1">
+      <x:c r="A110" s="34" t="str">
+        <x:v>Simone Luciani</x:v>
+      </x:c>
+      <x:c r="B110" s="34" t="str">
+        <x:v>simone luciani</x:v>
+      </x:c>
+      <x:c r="C110" s="34" t="str">
+        <x:v>35418</x:v>
+      </x:c>
+      <x:c r="D110" s="34" t="str">
+        <x:v>Simone Luciani</x:v>
+      </x:c>
+      <x:c r="E110" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/35418/simone-luciani</x:v>
+      </x:c>
+      <x:c r="F110" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/-Vn4TFt8V3slZWmYr8Vwlw__previewthumb/img/dTptvMSnOIpcZyFgWcGU3qIpmjg=/fit-in/300x320/filters:strip_icc()/pic3674677.jpg</x:v>
+      </x:c>
+      <x:c r="G110" s="34" t="str">
+        <x:v>assets/designers/35418.webp</x:v>
+      </x:c>
+      <x:c r="H110" s="34" t="str">
+        <x:v>3674677</x:v>
+      </x:c>
+      <x:c r="I110" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J110" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K110" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=35418&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L110" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/462941/entropy</x:v>
+      </x:c>
+      <x:c r="M110" s="34" t="str">
+        <x:v>462941</x:v>
+      </x:c>
+      <x:c r="N110" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=462941&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O110" s="34" t="str"/>
+    </x:row>
+    <x:row r="111" ht="22" customHeight="1">
+      <x:c r="A111" s="34" t="str">
+        <x:v>Stefan Stadler</x:v>
+      </x:c>
+      <x:c r="B111" s="34" t="str">
+        <x:v>stefan stadler</x:v>
+      </x:c>
+      <x:c r="C111" s="34" t="str">
+        <x:v>7391</x:v>
+      </x:c>
+      <x:c r="D111" s="34" t="str">
+        <x:v>Stefan Stadler</x:v>
+      </x:c>
+      <x:c r="E111" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/7391/stefan-stadler</x:v>
+      </x:c>
+      <x:c r="F111" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/RlK1wk7719uUMnvUfa-bCg__previewthumb/img/dI2LHegUnx3lFcTOaH5bY1laDQM=/fit-in/300x320/filters:strip_icc()/pic9706968.jpg</x:v>
+      </x:c>
+      <x:c r="G111" s="34" t="str">
+        <x:v>assets/designers/7391.webp</x:v>
+      </x:c>
+      <x:c r="H111" s="34" t="str">
+        <x:v>9706968</x:v>
+      </x:c>
+      <x:c r="I111" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J111" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K111" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=7391&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L111" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/64461/cuba-kanadische-botschaft</x:v>
+      </x:c>
+      <x:c r="M111" s="34" t="str">
+        <x:v>64461</x:v>
+      </x:c>
+      <x:c r="N111" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=64461&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O111" s="34" t="str"/>
+    </x:row>
+    <x:row r="112" ht="22" customHeight="1">
+      <x:c r="A112" s="34" t="str">
+        <x:v>Stefano Castelli</x:v>
+      </x:c>
+      <x:c r="B112" s="34" t="str">
+        <x:v>stefano castelli</x:v>
+      </x:c>
+      <x:c r="C112" s="34" t="str">
+        <x:v>8313</x:v>
+      </x:c>
+      <x:c r="D112" s="34" t="str">
+        <x:v>Stefano Castelli</x:v>
+      </x:c>
+      <x:c r="E112" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/8313/stefano-castelli</x:v>
+      </x:c>
+      <x:c r="F112" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/dwUogdBK_cUd1d5nLuoxAQ__previewthumb/img/QHHFUgLSne3Abk3YxgUWXCC4VrQ=/fit-in/300x320/filters:strip_icc()/pic327631.jpg</x:v>
+      </x:c>
+      <x:c r="G112" s="34" t="str">
+        <x:v>assets/designers/8313.webp</x:v>
+      </x:c>
+      <x:c r="H112" s="34" t="str">
+        <x:v>327631</x:v>
+      </x:c>
+      <x:c r="I112" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J112" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K112" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=8313&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L112" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/478511/opera-magna-the-eagle-and-the-lion</x:v>
+      </x:c>
+      <x:c r="M112" s="34" t="str">
+        <x:v>478511</x:v>
+      </x:c>
+      <x:c r="N112" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=478511&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O112" s="34" t="str"/>
+    </x:row>
+    <x:row r="113" ht="22" customHeight="1">
+      <x:c r="A113" s="34" t="str">
+        <x:v>Steven Aramini</x:v>
+      </x:c>
+      <x:c r="B113" s="34" t="str">
+        <x:v>steven aramini</x:v>
+      </x:c>
+      <x:c r="C113" s="34" t="str">
+        <x:v>73472</x:v>
+      </x:c>
+      <x:c r="D113" s="34" t="str">
+        <x:v>Steven Aramini</x:v>
+      </x:c>
+      <x:c r="E113" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/73472/steven-aramini</x:v>
+      </x:c>
+      <x:c r="F113" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/s2xl58ZCjzWYjLR-giZ0Kg__previewthumb/img/cKY5759xolyDlpvvlj4zhQ-s84I=/fit-in/300x320/filters:strip_icc()/pic3925412.jpg</x:v>
+      </x:c>
+      <x:c r="G113" s="34" t="str">
+        <x:v>assets/designers/73472.webp</x:v>
+      </x:c>
+      <x:c r="H113" s="34" t="str">
+        <x:v>3925412</x:v>
+      </x:c>
+      <x:c r="I113" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J113" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K113" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=73472&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L113" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/448546/fliptown-new-frontier</x:v>
+      </x:c>
+      <x:c r="M113" s="34" t="str">
+        <x:v>448546</x:v>
+      </x:c>
+      <x:c r="N113" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=448546&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O113" s="34" t="str"/>
+    </x:row>
+    <x:row r="114" ht="22" customHeight="1">
+      <x:c r="A114" s="34" t="str">
+        <x:v>Sönke Schmidt</x:v>
+      </x:c>
+      <x:c r="B114" s="34" t="str">
+        <x:v>sönke schmidt</x:v>
+      </x:c>
+      <x:c r="C114" s="34" t="str">
+        <x:v>145314</x:v>
+      </x:c>
+      <x:c r="D114" s="34" t="str">
+        <x:v>Sönke Schmidt</x:v>
+      </x:c>
+      <x:c r="E114" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/145314/sonke-schmidt</x:v>
+      </x:c>
+      <x:c r="F114" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/wIxScEadATqMjnMB2uy_qQ__previewthumb/img/EzfCgYlcpibYuhI-Ldfct3XAnYM=/fit-in/300x320/filters:strip_icc()/pic9583038.jpg</x:v>
+      </x:c>
+      <x:c r="G114" s="34" t="str">
+        <x:v>assets/designers/145314.webp</x:v>
+      </x:c>
+      <x:c r="H114" s="34" t="str">
+        <x:v>9583038</x:v>
+      </x:c>
+      <x:c r="I114" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J114" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K114" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=145314&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L114" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/454438/8-dragons</x:v>
+      </x:c>
+      <x:c r="M114" s="34" t="str">
+        <x:v>454438</x:v>
+      </x:c>
+      <x:c r="N114" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=454438&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O114" s="34" t="str"/>
+    </x:row>
+    <x:row r="115" ht="22" customHeight="1">
+      <x:c r="A115" s="34" t="str">
+        <x:v>T.K. King</x:v>
+      </x:c>
+      <x:c r="B115" s="34" t="str">
+        <x:v>t.k. king</x:v>
+      </x:c>
+      <x:c r="C115" s="34" t="str">
+        <x:v>129131</x:v>
+      </x:c>
+      <x:c r="D115" s="34" t="str">
+        <x:v>T.K. King</x:v>
+      </x:c>
+      <x:c r="E115" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/129131/tk-king</x:v>
+      </x:c>
+      <x:c r="F115" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/7KtUqEw1iHRUfocBwq94DQ__previewthumb/img/BsTJBXPbEQ8eWb-CIVBHzwpqwH0=/fit-in/300x320/filters:strip_icc()/pic7557085.jpg</x:v>
+      </x:c>
+      <x:c r="G115" s="34" t="str">
+        <x:v>assets/designers/129131.webp</x:v>
+      </x:c>
+      <x:c r="H115" s="34" t="str">
+        <x:v>7557085</x:v>
+      </x:c>
+      <x:c r="I115" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J115" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K115" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=129131&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L115" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/470410/galactic-cruise-perfect-planning-promo-card</x:v>
+      </x:c>
+      <x:c r="M115" s="34" t="str">
+        <x:v>470410</x:v>
+      </x:c>
+      <x:c r="N115" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=470410&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O115" s="34" t="str"/>
+    </x:row>
+    <x:row r="116" ht="22" customHeight="1">
+      <x:c r="A116" s="34" t="str">
+        <x:v>Tamsin Caesar</x:v>
+      </x:c>
+      <x:c r="B116" s="34" t="str">
+        <x:v>tamsin caesar</x:v>
+      </x:c>
+      <x:c r="C116" s="34" t="str">
+        <x:v>82932</x:v>
+      </x:c>
+      <x:c r="D116" s="34" t="str">
+        <x:v>Tamsin Caesar</x:v>
+      </x:c>
+      <x:c r="E116" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/82932/tamsin-caesar</x:v>
+      </x:c>
+      <x:c r="F116" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/du6uWI1nKkQH188hHqlZEQ__previewthumb/img/6_W2PiHjbvHSdQrYXwn2mswDams=/fit-in/300x320/filters:strip_icc()/pic6978705.jpg</x:v>
+      </x:c>
+      <x:c r="G116" s="34" t="str">
+        <x:v>assets/designers/82932.webp</x:v>
+      </x:c>
+      <x:c r="H116" s="34" t="str">
+        <x:v>6978705</x:v>
+      </x:c>
+      <x:c r="I116" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J116" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K116" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=82932&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L116" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/397788</x:v>
+      </x:c>
+      <x:c r="M116" s="34" t="str">
+        <x:v>397788</x:v>
+      </x:c>
+      <x:c r="N116" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=397788&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O116" s="34" t="str">
+        <x:v>原始遊戲 ID 324590 已依 README 已核對更正為 397788，以正確遊戲署名確認設計師身分</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" ht="22" customHeight="1">
+      <x:c r="A117" s="34" t="str">
+        <x:v>Thomas Mazzantini</x:v>
+      </x:c>
+      <x:c r="B117" s="34" t="str">
+        <x:v>thomas mazzantini</x:v>
+      </x:c>
+      <x:c r="C117" s="34" t="str">
+        <x:v>83890</x:v>
+      </x:c>
+      <x:c r="D117" s="34" t="str">
+        <x:v>Thomas Mazzantini</x:v>
+      </x:c>
+      <x:c r="E117" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/83890/thomas-mazzantini</x:v>
+      </x:c>
+      <x:c r="F117" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/SJX8jf8NlUwDI6enCOoqbg__previewthumb/img/Y5P0lzSPVVn1qFR2YyAKPSwFYSY=/fit-in/300x320/filters:strip_icc()/pic7245320.png</x:v>
+      </x:c>
+      <x:c r="G117" s="34" t="str">
+        <x:v>assets/designers/83890.webp</x:v>
+      </x:c>
+      <x:c r="H117" s="34" t="str">
+        <x:v>7245320</x:v>
+      </x:c>
+      <x:c r="I117" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J117" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K117" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=83890&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L117" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/224664/la-famiglia</x:v>
+      </x:c>
+      <x:c r="M117" s="34" t="str">
+        <x:v>224664</x:v>
+      </x:c>
+      <x:c r="N117" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=224664&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O117" s="34" t="str"/>
+    </x:row>
+    <x:row r="118" ht="22" customHeight="1">
+      <x:c r="A118" s="34" t="str">
+        <x:v>Thomas Vande Ginste</x:v>
+      </x:c>
+      <x:c r="B118" s="34" t="str">
+        <x:v>thomas vande ginste</x:v>
+      </x:c>
+      <x:c r="C118" s="34" t="str">
+        <x:v>57430</x:v>
+      </x:c>
+      <x:c r="D118" s="34" t="str">
+        <x:v>Thomas Vande Ginste</x:v>
+      </x:c>
+      <x:c r="E118" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/57430/thomas-vande-ginste</x:v>
+      </x:c>
+      <x:c r="F118" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/vKqCwR9Jxkxvy43hz4uK_Q__previewthumb/img/XyqMPnEzeSEMM-QIkCBrBshLtJI=/fit-in/300x320/filters:strip_icc()/pic1295833.jpg</x:v>
+      </x:c>
+      <x:c r="G118" s="34" t="str">
+        <x:v>assets/designers/57430.webp</x:v>
+      </x:c>
+      <x:c r="H118" s="34" t="str">
+        <x:v>1295833</x:v>
+      </x:c>
+      <x:c r="I118" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J118" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K118" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=57430&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L118" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/256997/perseverance-castaway-chronicles-episodes-1-and-2</x:v>
+      </x:c>
+      <x:c r="M118" s="34" t="str">
+        <x:v>256997</x:v>
+      </x:c>
+      <x:c r="N118" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=256997&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O118" s="34" t="str"/>
+    </x:row>
+    <x:row r="119" ht="22" customHeight="1">
+      <x:c r="A119" s="34" t="str">
+        <x:v>Tom Jolly</x:v>
+      </x:c>
+      <x:c r="B119" s="34" t="str">
+        <x:v>tom jolly</x:v>
+      </x:c>
+      <x:c r="C119" s="34" t="str">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="D119" s="34" t="str">
+        <x:v>Tom Jolly</x:v>
+      </x:c>
+      <x:c r="E119" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/222/tom-jolly</x:v>
+      </x:c>
+      <x:c r="F119" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/aCdvYVdx1srU1XzicdiF6g__previewthumb/img/o_MPgF0MlEEZEsaBYrN025GPlvA=/fit-in/300x320/filters:strip_icc()/pic1771453.jpg</x:v>
+      </x:c>
+      <x:c r="G119" s="34" t="str">
+        <x:v>assets/designers/222.webp</x:v>
+      </x:c>
+      <x:c r="H119" s="34" t="str">
+        <x:v>1771453</x:v>
+      </x:c>
+      <x:c r="I119" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J119" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K119" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=222&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L119" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/477064/light-speed-arena-dice-tower-sponsored-asteroid</x:v>
+      </x:c>
+      <x:c r="M119" s="34" t="str">
+        <x:v>477064</x:v>
+      </x:c>
+      <x:c r="N119" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=477064&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O119" s="34" t="str"/>
+    </x:row>
+    <x:row r="120" ht="22" customHeight="1">
+      <x:c r="A120" s="34" t="str">
+        <x:v>Tommaso Battista</x:v>
+      </x:c>
+      <x:c r="B120" s="34" t="str">
+        <x:v>tommaso battista</x:v>
+      </x:c>
+      <x:c r="C120" s="34" t="str">
+        <x:v>108836</x:v>
+      </x:c>
+      <x:c r="D120" s="34" t="str">
+        <x:v>Tommaso Battista</x:v>
+      </x:c>
+      <x:c r="E120" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/108836/tommaso-battista</x:v>
+      </x:c>
+      <x:c r="F120" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/4k0CQpLmyHFonFnzCtPxCQ__previewthumb/img/ohXBgB5oSJ0Sh83KI-9x87MJHbg=/fit-in/300x320/filters:strip_icc()/pic4098575.jpg</x:v>
+      </x:c>
+      <x:c r="G120" s="34" t="str">
+        <x:v>assets/designers/108836.webp</x:v>
+      </x:c>
+      <x:c r="H120" s="34" t="str">
+        <x:v>4098575</x:v>
+      </x:c>
+      <x:c r="I120" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J120" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K120" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=108836&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L120" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/462941/entropy</x:v>
+      </x:c>
+      <x:c r="M120" s="34" t="str">
+        <x:v>462941</x:v>
+      </x:c>
+      <x:c r="N120" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=462941&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O120" s="34" t="str"/>
+    </x:row>
+    <x:row r="121" ht="22" customHeight="1">
+      <x:c r="A121" s="34" t="str">
+        <x:v>Tomáš Uhlíř</x:v>
+      </x:c>
+      <x:c r="B121" s="34" t="str">
+        <x:v>tomáš uhlíř</x:v>
+      </x:c>
+      <x:c r="C121" s="34" t="str">
+        <x:v>9217</x:v>
+      </x:c>
+      <x:c r="D121" s="34" t="str">
+        <x:v>Tomáš Uhlíř</x:v>
+      </x:c>
+      <x:c r="E121" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/9217/tomas-uhlir</x:v>
+      </x:c>
+      <x:c r="F121" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/JAEu2L_V1bF6dT9Fd_1lIg__previewthumb/img/oX5WcpCusrI-lnCyDuFZbHaCcao=/fit-in/300x320/filters:strip_icc()/pic6454816.jpg</x:v>
+      </x:c>
+      <x:c r="G121" s="34" t="str">
+        <x:v>assets/designers/9217.webp</x:v>
+      </x:c>
+      <x:c r="H121" s="34" t="str">
+        <x:v>6454816</x:v>
+      </x:c>
+      <x:c r="I121" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J121" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K121" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=9217&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L121" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/306735/under-falling-skies</x:v>
+      </x:c>
+      <x:c r="M121" s="34" t="str">
+        <x:v>306735</x:v>
+      </x:c>
+      <x:c r="N121" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=306735&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O121" s="34" t="str"/>
+    </x:row>
+    <x:row r="122" ht="22" customHeight="1">
+      <x:c r="A122" s="34" t="str">
+        <x:v>Tyler Cheves</x:v>
+      </x:c>
+      <x:c r="B122" s="34" t="str">
+        <x:v>tyler cheves</x:v>
+      </x:c>
+      <x:c r="C122" s="34" t="str">
+        <x:v>105974</x:v>
+      </x:c>
+      <x:c r="D122" s="34" t="str">
+        <x:v>Tyler Cheves</x:v>
+      </x:c>
+      <x:c r="E122" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/105974/tyler-cheves</x:v>
+      </x:c>
+      <x:c r="F122" s="34" t="str"/>
+      <x:c r="G122" s="34" t="str"/>
+      <x:c r="H122" s="34" t="str">
+        <x:v>1657690</x:v>
+      </x:c>
+      <x:c r="I122" s="34" t="str">
+        <x:v>no-image</x:v>
+      </x:c>
+      <x:c r="J122" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K122" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=105974&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L122" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/439093/red-dog-junction</x:v>
+      </x:c>
+      <x:c r="M122" s="34" t="str">
+        <x:v>439093</x:v>
+      </x:c>
+      <x:c r="N122" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=439093&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O122" s="34" t="str">
+        <x:v>BGG 設計師個人頁使用通用缺圖圖示；BGG 個人相簿查核：圖庫無圖片；相簿來源：https://api.geekdo.com/api/images?ajax=1&amp;gallery=all&amp;nosession=1&amp;objectid=105974&amp;objecttype=person&amp;pageid=1&amp;showcount=10&amp;sort=hot</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" ht="22" customHeight="1">
+      <x:c r="A123" s="34" t="str">
+        <x:v>Uwe Rosenberg</x:v>
+      </x:c>
+      <x:c r="B123" s="34" t="str">
+        <x:v>uwe rosenberg</x:v>
+      </x:c>
+      <x:c r="C123" s="34" t="str">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D123" s="34" t="str">
+        <x:v>Uwe Rosenberg</x:v>
+      </x:c>
+      <x:c r="E123" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/10/uwe-rosenberg</x:v>
+      </x:c>
+      <x:c r="F123" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/3LC1yhKGgJsQjmnzpgpQQg__previewthumb/img/LOqHXliIX8ypy0i8zBgAlBMLSt4=/fit-in/300x320/filters:strip_icc()/pic537818.jpg</x:v>
+      </x:c>
+      <x:c r="G123" s="34" t="str">
+        <x:v>assets/designers/10.webp</x:v>
+      </x:c>
+      <x:c r="H123" s="34" t="str">
+        <x:v>537818</x:v>
+      </x:c>
+      <x:c r="I123" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J123" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K123" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=10&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L123" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/450923/the-danes</x:v>
+      </x:c>
+      <x:c r="M123" s="34" t="str">
+        <x:v>450923</x:v>
+      </x:c>
+      <x:c r="N123" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=450923&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O123" s="34" t="str"/>
+    </x:row>
+    <x:row r="124" ht="22" customHeight="1">
+      <x:c r="A124" s="34" t="str">
+        <x:v>Vangelis Efthimiou</x:v>
+      </x:c>
+      <x:c r="B124" s="34" t="str">
+        <x:v>vangelis efthimiou</x:v>
+      </x:c>
+      <x:c r="C124" s="34" t="str">
+        <x:v>141460</x:v>
+      </x:c>
+      <x:c r="D124" s="34" t="str">
+        <x:v>Vangelis Efthimiou</x:v>
+      </x:c>
+      <x:c r="E124" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/141460/vangelis-efthimiou</x:v>
+      </x:c>
+      <x:c r="F124" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/3YyLARZ0qPNfc5pfXpTRQg__previewthumb/img/b1h4BhdZmjmmXKDlUNJ4OLxsub4=/fit-in/300x320/filters:strip_icc()/pic7250660.jpg</x:v>
+      </x:c>
+      <x:c r="G124" s="34" t="str">
+        <x:v>assets/designers/141460.webp</x:v>
+      </x:c>
+      <x:c r="H124" s="34" t="str">
+        <x:v>7250660</x:v>
+      </x:c>
+      <x:c r="I124" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J124" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K124" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=141460&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L124" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/448158/vacations-to-greek-islands</x:v>
+      </x:c>
+      <x:c r="M124" s="34" t="str">
+        <x:v>448158</x:v>
+      </x:c>
+      <x:c r="N124" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=448158&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O124" s="34" t="str"/>
+    </x:row>
+    <x:row r="125" ht="22" customHeight="1">
+      <x:c r="A125" s="34" t="str">
+        <x:v>Viktor Péter</x:v>
+      </x:c>
+      <x:c r="B125" s="34" t="str">
+        <x:v>viktor péter</x:v>
+      </x:c>
+      <x:c r="C125" s="34" t="str">
+        <x:v>76578</x:v>
+      </x:c>
+      <x:c r="D125" s="34" t="str">
+        <x:v>Viktor Péter</x:v>
+      </x:c>
+      <x:c r="E125" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/76578/viktor-peter</x:v>
+      </x:c>
+      <x:c r="F125" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/B_amc7hDA0O7OWKphLP-pw__previewthumb/img/V3DpnZcVuDDtJXVj8siU1jnFREM=/fit-in/300x320/filters:strip_icc()/pic8641924.jpg</x:v>
+      </x:c>
+      <x:c r="G125" s="34" t="str">
+        <x:v>assets/designers/76578.webp</x:v>
+      </x:c>
+      <x:c r="H125" s="34" t="str">
+        <x:v>8641924</x:v>
+      </x:c>
+      <x:c r="I125" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J125" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K125" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=76578&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L125" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/256997/perseverance-castaway-chronicles-episodes-1-and-2</x:v>
+      </x:c>
+      <x:c r="M125" s="34" t="str">
+        <x:v>256997</x:v>
+      </x:c>
+      <x:c r="N125" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=256997&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O125" s="34" t="str"/>
+    </x:row>
+    <x:row r="126" ht="22" customHeight="1">
+      <x:c r="A126" s="34" t="str">
+        <x:v>Vital Lacerda</x:v>
+      </x:c>
+      <x:c r="B126" s="34" t="str">
+        <x:v>vital lacerda</x:v>
+      </x:c>
+      <x:c r="C126" s="34" t="str">
+        <x:v>12396</x:v>
+      </x:c>
+      <x:c r="D126" s="34" t="str">
+        <x:v>Vital Lacerda</x:v>
+      </x:c>
+      <x:c r="E126" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/12396/vital-lacerda</x:v>
+      </x:c>
+      <x:c r="F126" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/1uyXWwYFCH_gTi30zYLalw__previewthumb/img/b8dkO4U5vymvF6uJAcmmAJy6sVE=/fit-in/300x320/filters:strip_icc()/pic3546633.jpg</x:v>
+      </x:c>
+      <x:c r="G126" s="34" t="str">
+        <x:v>assets/designers/12396.webp</x:v>
+      </x:c>
+      <x:c r="H126" s="34" t="str">
+        <x:v>3546633</x:v>
+      </x:c>
+      <x:c r="I126" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J126" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K126" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=12396&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L126" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/237179/weather-machine</x:v>
+      </x:c>
+      <x:c r="M126" s="34" t="str">
+        <x:v>237179</x:v>
+      </x:c>
+      <x:c r="N126" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=237179&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O126" s="34" t="str"/>
+    </x:row>
+    <x:row r="127" ht="22" customHeight="1">
+      <x:c r="A127" s="34" t="str">
+        <x:v>Vladimír Suchý</x:v>
+      </x:c>
+      <x:c r="B127" s="34" t="str">
+        <x:v>vladimír suchý</x:v>
+      </x:c>
+      <x:c r="C127" s="34" t="str">
+        <x:v>9307</x:v>
+      </x:c>
+      <x:c r="D127" s="34" t="str">
+        <x:v>Vladimír Suchý</x:v>
+      </x:c>
+      <x:c r="E127" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/9307/vladimir-suchy</x:v>
+      </x:c>
+      <x:c r="F127" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/oFBlHBVKCQVc7NuLxPE7Xg__previewthumb/img/1zeWj3KDNtcozjRjK-xEqtOQhKE=/fit-in/300x320/filters:strip_icc()/pic582961.jpg</x:v>
+      </x:c>
+      <x:c r="G127" s="34" t="str">
+        <x:v>assets/designers/9307.webp</x:v>
+      </x:c>
+      <x:c r="H127" s="34" t="str">
+        <x:v>582961</x:v>
+      </x:c>
+      <x:c r="I127" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J127" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K127" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=9307&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L127" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/308765/praga-caput-regni</x:v>
+      </x:c>
+      <x:c r="M127" s="34" t="str">
+        <x:v>308765</x:v>
+      </x:c>
+      <x:c r="N127" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=308765&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O127" s="34" t="str"/>
+    </x:row>
+    <x:row r="128" ht="22" customHeight="1">
+      <x:c r="A128" s="34" t="str">
+        <x:v>Wai Yee</x:v>
+      </x:c>
+      <x:c r="B128" s="34" t="str">
+        <x:v>wai yee</x:v>
+      </x:c>
+      <x:c r="C128" s="34" t="str">
+        <x:v>110589</x:v>
+      </x:c>
+      <x:c r="D128" s="34" t="str">
+        <x:v>Wai Yee</x:v>
+      </x:c>
+      <x:c r="E128" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/110589/wai-yee</x:v>
+      </x:c>
+      <x:c r="F128" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/m9HJVyYqxXxNgEf_znYgTg__previewthumb/img/mCuKL503tiCoAoM20yg4FyqwrLk=/fit-in/300x320/filters:strip_icc()/pic4209808.jpg</x:v>
+      </x:c>
+      <x:c r="G128" s="34" t="str">
+        <x:v>assets/designers/110589.webp</x:v>
+      </x:c>
+      <x:c r="H128" s="34" t="str">
+        <x:v>4209808</x:v>
+      </x:c>
+      <x:c r="I128" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J128" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K128" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=110589&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L128" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/292126/excavation-earth</x:v>
+      </x:c>
+      <x:c r="M128" s="34" t="str">
+        <x:v>292126</x:v>
+      </x:c>
+      <x:c r="N128" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=292126&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O128" s="34" t="str"/>
+    </x:row>
+    <x:row r="129" ht="22" customHeight="1">
+      <x:c r="A129" s="34" t="str">
+        <x:v>Wolf Plancke</x:v>
+      </x:c>
+      <x:c r="B129" s="34" t="str">
+        <x:v>wolf plancke</x:v>
+      </x:c>
+      <x:c r="C129" s="34" t="str">
+        <x:v>57202</x:v>
+      </x:c>
+      <x:c r="D129" s="34" t="str">
+        <x:v>Wolf Plancke</x:v>
+      </x:c>
+      <x:c r="E129" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/57202/wolf-plancke</x:v>
+      </x:c>
+      <x:c r="F129" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/d0yZIYNR6JdmdP1lUc12sA__previewthumb/img/tRT9mnMgS_K05bQyfHbj9z_q1VI=/fit-in/300x320/filters:strip_icc()/pic1295490.jpg</x:v>
+      </x:c>
+      <x:c r="G129" s="34" t="str">
+        <x:v>assets/designers/57202.webp</x:v>
+      </x:c>
+      <x:c r="H129" s="34" t="str">
+        <x:v>1295490</x:v>
+      </x:c>
+      <x:c r="I129" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J129" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K129" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=57202&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L129" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/256997/perseverance-castaway-chronicles-episodes-1-and-2</x:v>
+      </x:c>
+      <x:c r="M129" s="34" t="str">
+        <x:v>256997</x:v>
+      </x:c>
+      <x:c r="N129" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=256997&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O129" s="34" t="str"/>
+    </x:row>
+    <x:row r="130" ht="22" customHeight="1">
+      <x:c r="A130" s="34" t="str">
+        <x:v>Xavier Violeau</x:v>
+      </x:c>
+      <x:c r="B130" s="34" t="str">
+        <x:v>xavier violeau</x:v>
+      </x:c>
+      <x:c r="C130" s="34" t="str">
+        <x:v>127496</x:v>
+      </x:c>
+      <x:c r="D130" s="34" t="str">
+        <x:v>Xavier Violeau</x:v>
+      </x:c>
+      <x:c r="E130" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/127496/xavier-violeau</x:v>
+      </x:c>
+      <x:c r="F130" s="34" t="str"/>
+      <x:c r="G130" s="34" t="str"/>
+      <x:c r="H130" s="34" t="str">
+        <x:v>1657690</x:v>
+      </x:c>
+      <x:c r="I130" s="34" t="str">
+        <x:v>no-image</x:v>
+      </x:c>
+      <x:c r="J130" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K130" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=127496&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L130" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/473012/1953-everest</x:v>
+      </x:c>
+      <x:c r="M130" s="34" t="str">
+        <x:v>473012</x:v>
+      </x:c>
+      <x:c r="N130" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=473012&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O130" s="34" t="str">
+        <x:v>BGG 設計師個人頁使用通用缺圖圖示；BGG 個人相簿查核：圖庫無圖片；相簿來源：https://api.geekdo.com/api/images?ajax=1&amp;gallery=all&amp;nosession=1&amp;objectid=127496&amp;objecttype=person&amp;pageid=1&amp;showcount=10&amp;sort=hot</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131" ht="22" customHeight="1">
+      <x:c r="A131" s="34" t="str">
+        <x:v>Zac Dixon</x:v>
+      </x:c>
+      <x:c r="B131" s="34" t="str">
+        <x:v>zac dixon</x:v>
+      </x:c>
+      <x:c r="C131" s="34" t="str">
+        <x:v>137869</x:v>
+      </x:c>
+      <x:c r="D131" s="34" t="str">
+        <x:v>Zac Dixon</x:v>
+      </x:c>
+      <x:c r="E131" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/137869/zac-dixon</x:v>
+      </x:c>
+      <x:c r="F131" s="34" t="str"/>
+      <x:c r="G131" s="34" t="str"/>
+      <x:c r="H131" s="34" t="str">
+        <x:v>1657690</x:v>
+      </x:c>
+      <x:c r="I131" s="34" t="str">
+        <x:v>no-image</x:v>
+      </x:c>
+      <x:c r="J131" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K131" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=137869&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L131" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/270239/moonrakers</x:v>
+      </x:c>
+      <x:c r="M131" s="34" t="str">
+        <x:v>270239</x:v>
+      </x:c>
+      <x:c r="N131" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=270239&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O131" s="34" t="str">
+        <x:v>BGG 設計師個人頁使用通用缺圖圖示；BGG 個人相簿查核：圖庫無圖片；相簿來源：https://api.geekdo.com/api/images?ajax=1&amp;gallery=all&amp;nosession=1&amp;objectid=137869&amp;objecttype=person&amp;pageid=1&amp;showcount=10&amp;sort=hot</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132" ht="22" customHeight="1">
+      <x:c r="A132" s="34" t="str">
+        <x:v>Zach Smith</x:v>
+      </x:c>
+      <x:c r="B132" s="34" t="str">
+        <x:v>zach smith</x:v>
+      </x:c>
+      <x:c r="C132" s="34" t="str">
+        <x:v>133311</x:v>
+      </x:c>
+      <x:c r="D132" s="34" t="str">
+        <x:v>Zach Smith</x:v>
+      </x:c>
+      <x:c r="E132" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/133311/zach-smith</x:v>
+      </x:c>
+      <x:c r="F132" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/X0P5Tv9vktKX5-Dstf0VhA__previewthumb/img/vZzealoHLiHtrmUH3zBJ4IYMJhM=/fit-in/300x320/filters:strip_icc()/pic5928504.jpg</x:v>
+      </x:c>
+      <x:c r="G132" s="34" t="str">
+        <x:v>assets/designers/133311.webp</x:v>
+      </x:c>
+      <x:c r="H132" s="34" t="str">
+        <x:v>5928504</x:v>
+      </x:c>
+      <x:c r="I132" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J132" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K132" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=133311&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L132" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/453699/the-great-sea</x:v>
+      </x:c>
+      <x:c r="M132" s="34" t="str">
+        <x:v>453699</x:v>
+      </x:c>
+      <x:c r="N132" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=453699&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O132" s="34" t="str"/>
+    </x:row>
+    <x:row r="133" ht="22" customHeight="1">
+      <x:c r="A133" s="34" t="str">
+        <x:v>Åsmund Svensson</x:v>
+      </x:c>
+      <x:c r="B133" s="34" t="str">
+        <x:v>åsmund svensson</x:v>
+      </x:c>
+      <x:c r="C133" s="34" t="str">
+        <x:v>134281</x:v>
+      </x:c>
+      <x:c r="D133" s="34" t="str">
+        <x:v>Åsmund Svensson</x:v>
+      </x:c>
+      <x:c r="E133" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgamedesigner/134281/asmund-svensson</x:v>
+      </x:c>
+      <x:c r="F133" s="34" t="str">
+        <x:v>https://cf.geekdo-images.com/jgHXTJsZqkoqJfDV6dzK0g__previewthumb/img/gU_D_QrjKkPbMwIU5TXd3bwJYno=/fit-in/300x320/filters:strip_icc()/pic6065972.png</x:v>
+      </x:c>
+      <x:c r="G133" s="34" t="str">
+        <x:v>assets/designers/134281.webp</x:v>
+      </x:c>
+      <x:c r="H133" s="34" t="str">
+        <x:v>6065972</x:v>
+      </x:c>
+      <x:c r="I133" s="34" t="str">
+        <x:v>ok</x:v>
+      </x:c>
+      <x:c r="J133" s="2" t="d">
+        <x:v>2026-10-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="K133" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=134281&amp;objecttype=person</x:v>
+      </x:c>
+      <x:c r="L133" s="34" t="str">
+        <x:v>https://boardgamegeek.com/boardgame/461255/wild-world</x:v>
+      </x:c>
+      <x:c r="M133" s="34" t="str">
+        <x:v>461255</x:v>
+      </x:c>
+      <x:c r="N133" s="34" t="str">
+        <x:v>https://api.geekdo.com/api/geekitems?objectid=461255&amp;objecttype=thing</x:v>
+      </x:c>
+      <x:c r="O133" s="34" t="str"/>
+    </x:row>
+  </x:sheetData>
+  <x:autoFilter ref="A1:O133"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>